--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-07-18.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-07-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3337"/>
+  <dimension ref="A1:G3220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87127,30 +87127,22 @@
     <row r="3099">
       <c r="A3099" t="inlineStr">
         <is>
-          <t>2025-07-08 15:30:00+05:30</t>
+          <t>2025-07-08 18:25:00+05:30</t>
         </is>
       </c>
       <c r="B3099" t="inlineStr">
         <is>
-          <t>NFIB Business Optimism IndexJUN</t>
+          <t>Used Car Prices MoMJUN</t>
         </is>
       </c>
       <c r="C3099" t="inlineStr"/>
       <c r="D3099" t="inlineStr">
         <is>
-          <t>98.8</t>
-        </is>
-      </c>
-      <c r="E3099" t="inlineStr">
-        <is>
-          <t>98.7</t>
-        </is>
-      </c>
-      <c r="F3099" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
+          <t>-1.4%</t>
+        </is>
+      </c>
+      <c r="E3099" t="inlineStr"/>
+      <c r="F3099" t="inlineStr"/>
       <c r="G3099" t="n">
         <v>3</v>
       </c>
@@ -87163,19 +87155,19 @@
       </c>
       <c r="B3100" t="inlineStr">
         <is>
-          <t>Redbook YoYJUL/05</t>
+          <t>Used Car Prices YoYJUN</t>
         </is>
       </c>
       <c r="C3100" t="inlineStr"/>
       <c r="D3100" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E3100" t="inlineStr"/>
       <c r="F3100" t="inlineStr"/>
       <c r="G3100" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3101">
@@ -87186,13 +87178,13 @@
       </c>
       <c r="B3101" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMJUN</t>
+          <t>Redbook YoYJUL/05</t>
         </is>
       </c>
       <c r="C3101" t="inlineStr"/>
       <c r="D3101" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="E3101" t="inlineStr"/>
@@ -87204,45 +87196,49 @@
     <row r="3102">
       <c r="A3102" t="inlineStr">
         <is>
-          <t>2025-07-08 18:25:00+05:30</t>
+          <t>2025-07-08 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B3102" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYJUN</t>
+          <t>Used Car Prices MoMJUN</t>
         </is>
       </c>
       <c r="C3102" t="inlineStr"/>
       <c r="D3102" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="E3102" t="inlineStr"/>
       <c r="F3102" t="inlineStr"/>
       <c r="G3102" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3103">
       <c r="A3103" t="inlineStr">
         <is>
-          <t>2025-07-08 18:25:00+05:30</t>
+          <t>2025-07-08 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B3103" t="inlineStr">
         <is>
-          <t>Redbook YoYJUL/05</t>
+          <t>Consumer Inflation ExpectationsJUN</t>
         </is>
       </c>
       <c r="C3103" t="inlineStr"/>
       <c r="D3103" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E3103" t="inlineStr"/>
-      <c r="F3103" t="inlineStr"/>
+      <c r="F3103" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="G3103" t="n">
         <v>3</v>
       </c>
@@ -87255,21 +87251,17 @@
       </c>
       <c r="B3104" t="inlineStr">
         <is>
-          <t>Consumer Inflation ExpectationsJUN</t>
+          <t>Used Car Prices YoYJUN</t>
         </is>
       </c>
       <c r="C3104" t="inlineStr"/>
       <c r="D3104" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E3104" t="inlineStr"/>
-      <c r="F3104" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="F3104" t="inlineStr"/>
       <c r="G3104" t="n">
         <v>3</v>
       </c>
@@ -87277,18 +87269,18 @@
     <row r="3105">
       <c r="A3105" t="inlineStr">
         <is>
-          <t>2025-07-08 20:30:00+05:30</t>
+          <t>2025-07-08 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B3105" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMJUN</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C3105" t="inlineStr"/>
       <c r="D3105" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>3.94%</t>
         </is>
       </c>
       <c r="E3105" t="inlineStr"/>
@@ -87300,26 +87292,22 @@
     <row r="3106">
       <c r="A3106" t="inlineStr">
         <is>
-          <t>2025-07-08 20:30:00+05:30</t>
+          <t>2025-07-08 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B3106" t="inlineStr">
         <is>
-          <t>Consumer Inflation ExpectationsJUN</t>
+          <t>Used Car Prices MoMJUN</t>
         </is>
       </c>
       <c r="C3106" t="inlineStr"/>
       <c r="D3106" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="E3106" t="inlineStr"/>
-      <c r="F3106" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="F3106" t="inlineStr"/>
       <c r="G3106" t="n">
         <v>3</v>
       </c>
@@ -87327,7 +87315,7 @@
     <row r="3107">
       <c r="A3107" t="inlineStr">
         <is>
-          <t>2025-07-08 20:30:00+05:30</t>
+          <t>2025-07-08 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B3107" t="inlineStr">
@@ -87350,18 +87338,18 @@
     <row r="3108">
       <c r="A3108" t="inlineStr">
         <is>
-          <t>2025-07-08 21:00:00+05:30</t>
+          <t>2025-07-08 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B3108" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>3-Year Note Auction</t>
         </is>
       </c>
       <c r="C3108" t="inlineStr"/>
       <c r="D3108" t="inlineStr">
         <is>
-          <t>3.94%</t>
+          <t>3.972%</t>
         </is>
       </c>
       <c r="E3108" t="inlineStr"/>
@@ -87373,18 +87361,18 @@
     <row r="3109">
       <c r="A3109" t="inlineStr">
         <is>
-          <t>2025-07-08 21:00:00+05:30</t>
+          <t>2025-07-08 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B3109" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Used Car Prices MoMJUN</t>
         </is>
       </c>
       <c r="C3109" t="inlineStr"/>
       <c r="D3109" t="inlineStr">
         <is>
-          <t>3.94%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="E3109" t="inlineStr"/>
@@ -87396,18 +87384,18 @@
     <row r="3110">
       <c r="A3110" t="inlineStr">
         <is>
-          <t>2025-07-08 21:00:00+05:30</t>
+          <t>2025-07-08 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B3110" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMJUN</t>
+          <t>Used Car Prices YoYJUN</t>
         </is>
       </c>
       <c r="C3110" t="inlineStr"/>
       <c r="D3110" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E3110" t="inlineStr"/>
@@ -87419,22 +87407,30 @@
     <row r="3111">
       <c r="A3111" t="inlineStr">
         <is>
-          <t>2025-07-08 21:00:00+05:30</t>
+          <t>2025-07-09 00:30:00+05:30</t>
         </is>
       </c>
       <c r="B3111" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYJUN</t>
+          <t>Consumer Credit ChangeMAY</t>
         </is>
       </c>
       <c r="C3111" t="inlineStr"/>
       <c r="D3111" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="E3111" t="inlineStr"/>
-      <c r="F3111" t="inlineStr"/>
+          <t>$17.87B</t>
+        </is>
+      </c>
+      <c r="E3111" t="inlineStr">
+        <is>
+          <t>$10.5B</t>
+        </is>
+      </c>
+      <c r="F3111" t="inlineStr">
+        <is>
+          <t>$12.1B</t>
+        </is>
+      </c>
       <c r="G3111" t="n">
         <v>3</v>
       </c>
@@ -87442,64 +87438,64 @@
     <row r="3112">
       <c r="A3112" t="inlineStr">
         <is>
-          <t>2025-07-08 22:30:00+05:30</t>
+          <t>2025-07-09 02:00:00+05:30</t>
         </is>
       </c>
       <c r="B3112" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYJUN</t>
+          <t>API Crude Oil Stock ChangeJUL/04</t>
         </is>
       </c>
       <c r="C3112" t="inlineStr"/>
       <c r="D3112" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.680M</t>
         </is>
       </c>
       <c r="E3112" t="inlineStr"/>
       <c r="F3112" t="inlineStr"/>
       <c r="G3112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3113">
       <c r="A3113" t="inlineStr">
         <is>
-          <t>2025-07-08 22:30:00+05:30</t>
+          <t>2025-07-09 16:30:00+05:30</t>
         </is>
       </c>
       <c r="B3113" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMJUN</t>
+          <t>MBA 30-Year Mortgage RateJUL/04</t>
         </is>
       </c>
       <c r="C3113" t="inlineStr"/>
       <c r="D3113" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>6.79%</t>
         </is>
       </c>
       <c r="E3113" t="inlineStr"/>
       <c r="F3113" t="inlineStr"/>
       <c r="G3113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3114">
       <c r="A3114" t="inlineStr">
         <is>
-          <t>2025-07-08 22:30:00+05:30</t>
+          <t>2025-07-09 16:30:00+05:30</t>
         </is>
       </c>
       <c r="B3114" t="inlineStr">
         <is>
-          <t>3-Year Note Auction</t>
+          <t>MBA Mortgage Refinance IndexJUL/04</t>
         </is>
       </c>
       <c r="C3114" t="inlineStr"/>
       <c r="D3114" t="inlineStr">
         <is>
-          <t>3.972%</t>
+          <t>759.7</t>
         </is>
       </c>
       <c r="E3114" t="inlineStr"/>
@@ -87511,18 +87507,18 @@
     <row r="3115">
       <c r="A3115" t="inlineStr">
         <is>
-          <t>2025-07-08 22:30:00+05:30</t>
+          <t>2025-07-09 16:30:00+05:30</t>
         </is>
       </c>
       <c r="B3115" t="inlineStr">
         <is>
-          <t>3-Year Note Auction</t>
+          <t>MBA Mortgage Market IndexJUL/04</t>
         </is>
       </c>
       <c r="C3115" t="inlineStr"/>
       <c r="D3115" t="inlineStr">
         <is>
-          <t>3.972%</t>
+          <t>257.5</t>
         </is>
       </c>
       <c r="E3115" t="inlineStr"/>
@@ -87534,18 +87530,18 @@
     <row r="3116">
       <c r="A3116" t="inlineStr">
         <is>
-          <t>2025-07-08 22:30:00+05:30</t>
+          <t>2025-07-09 16:30:00+05:30</t>
         </is>
       </c>
       <c r="B3116" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMJUN</t>
+          <t>MBA Purchase IndexJUL/04</t>
         </is>
       </c>
       <c r="C3116" t="inlineStr"/>
       <c r="D3116" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>165.3</t>
         </is>
       </c>
       <c r="E3116" t="inlineStr"/>
@@ -87557,18 +87553,18 @@
     <row r="3117">
       <c r="A3117" t="inlineStr">
         <is>
-          <t>2025-07-08 22:30:00+05:30</t>
+          <t>2025-07-09 16:30:00+05:30</t>
         </is>
       </c>
       <c r="B3117" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYJUN</t>
+          <t>MBA Mortgage ApplicationsJUL/04</t>
         </is>
       </c>
       <c r="C3117" t="inlineStr"/>
       <c r="D3117" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="E3117" t="inlineStr"/>
@@ -87580,28 +87576,28 @@
     <row r="3118">
       <c r="A3118" t="inlineStr">
         <is>
-          <t>2025-07-09 00:30:00+05:30</t>
+          <t>2025-07-09 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B3118" t="inlineStr">
         <is>
-          <t>Consumer Credit ChangeMAY</t>
+          <t>Wholesale Inventories MoMMAY</t>
         </is>
       </c>
       <c r="C3118" t="inlineStr"/>
       <c r="D3118" t="inlineStr">
         <is>
-          <t>$17.87B</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E3118" t="inlineStr">
         <is>
-          <t>$10.5B</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F3118" t="inlineStr">
         <is>
-          <t>$12.1B</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="G3118" t="n">
@@ -87611,30 +87607,22 @@
     <row r="3119">
       <c r="A3119" t="inlineStr">
         <is>
-          <t>2025-07-09 00:30:00+05:30</t>
+          <t>2025-07-09 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B3119" t="inlineStr">
         <is>
-          <t>Consumer Credit ChangeMAY</t>
+          <t>EIA Distillate Fuel Production ChangeJUL/04</t>
         </is>
       </c>
       <c r="C3119" t="inlineStr"/>
       <c r="D3119" t="inlineStr">
         <is>
-          <t>$17.87B</t>
-        </is>
-      </c>
-      <c r="E3119" t="inlineStr">
-        <is>
-          <t>$10.5B</t>
-        </is>
-      </c>
-      <c r="F3119" t="inlineStr">
-        <is>
-          <t>$12.1B</t>
-        </is>
-      </c>
+          <t>0.245M</t>
+        </is>
+      </c>
+      <c r="E3119" t="inlineStr"/>
+      <c r="F3119" t="inlineStr"/>
       <c r="G3119" t="n">
         <v>3</v>
       </c>
@@ -87642,18 +87630,18 @@
     <row r="3120">
       <c r="A3120" t="inlineStr">
         <is>
-          <t>2025-07-09 02:00:00+05:30</t>
+          <t>2025-07-09 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B3120" t="inlineStr">
         <is>
-          <t>API Crude Oil Stock ChangeJUL/04</t>
+          <t>EIA Gasoline Stocks ChangeJUL/04</t>
         </is>
       </c>
       <c r="C3120" t="inlineStr"/>
       <c r="D3120" t="inlineStr">
         <is>
-          <t>0.680M</t>
+          <t>4.188M</t>
         </is>
       </c>
       <c r="E3120" t="inlineStr"/>
@@ -87665,41 +87653,41 @@
     <row r="3121">
       <c r="A3121" t="inlineStr">
         <is>
-          <t>2025-07-09 02:00:00+05:30</t>
+          <t>2025-07-09 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B3121" t="inlineStr">
         <is>
-          <t>API Crude Oil Stock ChangeJUL/04</t>
+          <t>EIA Crude Oil Imports ChangeJUL/04</t>
         </is>
       </c>
       <c r="C3121" t="inlineStr"/>
       <c r="D3121" t="inlineStr">
         <is>
-          <t>0.680M</t>
+          <t>2.94M</t>
         </is>
       </c>
       <c r="E3121" t="inlineStr"/>
       <c r="F3121" t="inlineStr"/>
       <c r="G3121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3122">
       <c r="A3122" t="inlineStr">
         <is>
-          <t>2025-07-09 16:30:00+05:30</t>
+          <t>2025-07-09 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B3122" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJUL/04</t>
+          <t>EIA Crude Oil Stocks ChangeJUL/04</t>
         </is>
       </c>
       <c r="C3122" t="inlineStr"/>
       <c r="D3122" t="inlineStr">
         <is>
-          <t>6.79%</t>
+          <t>3.845M</t>
         </is>
       </c>
       <c r="E3122" t="inlineStr"/>
@@ -87711,18 +87699,18 @@
     <row r="3123">
       <c r="A3123" t="inlineStr">
         <is>
-          <t>2025-07-09 16:30:00+05:30</t>
+          <t>2025-07-09 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B3123" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJUL/04</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJUL/04</t>
         </is>
       </c>
       <c r="C3123" t="inlineStr"/>
       <c r="D3123" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>-1.493M</t>
         </is>
       </c>
       <c r="E3123" t="inlineStr"/>
@@ -87734,18 +87722,18 @@
     <row r="3124">
       <c r="A3124" t="inlineStr">
         <is>
-          <t>2025-07-09 16:30:00+05:30</t>
+          <t>2025-07-09 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B3124" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJUL/04</t>
+          <t>EIA Distillate Stocks ChangeJUL/04</t>
         </is>
       </c>
       <c r="C3124" t="inlineStr"/>
       <c r="D3124" t="inlineStr">
         <is>
-          <t>257.5</t>
+          <t>-1.71M</t>
         </is>
       </c>
       <c r="E3124" t="inlineStr"/>
@@ -87757,21 +87745,21 @@
     <row r="3125">
       <c r="A3125" t="inlineStr">
         <is>
-          <t>2025-07-09 16:30:00+05:30</t>
+          <t>2025-07-09 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B3125" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJUL/04</t>
+          <t>NY Fed Treasury Purchases Bill 0 to 1 yrs</t>
         </is>
       </c>
       <c r="C3125" t="inlineStr"/>
-      <c r="D3125" t="inlineStr">
-        <is>
-          <t>759.7</t>
-        </is>
-      </c>
-      <c r="E3125" t="inlineStr"/>
+      <c r="D3125" t="inlineStr"/>
+      <c r="E3125" t="inlineStr">
+        <is>
+          <t>$75 million</t>
+        </is>
+      </c>
       <c r="F3125" t="inlineStr"/>
       <c r="G3125" t="n">
         <v>3</v>
@@ -87780,18 +87768,18 @@
     <row r="3126">
       <c r="A3126" t="inlineStr">
         <is>
-          <t>2025-07-09 16:30:00+05:30</t>
+          <t>2025-07-09 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B3126" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJUL/04</t>
+          <t>EIA Heating Oil Stocks ChangeJUL/04</t>
         </is>
       </c>
       <c r="C3126" t="inlineStr"/>
       <c r="D3126" t="inlineStr">
         <is>
-          <t>165.3</t>
+          <t>-0.202M</t>
         </is>
       </c>
       <c r="E3126" t="inlineStr"/>
@@ -87803,41 +87791,41 @@
     <row r="3127">
       <c r="A3127" t="inlineStr">
         <is>
-          <t>2025-07-09 16:30:00+05:30</t>
+          <t>2025-07-09 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B3127" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJUL/04</t>
+          <t>EIA Refinery Crude Runs ChangeJUL/04</t>
         </is>
       </c>
       <c r="C3127" t="inlineStr"/>
       <c r="D3127" t="inlineStr">
         <is>
-          <t>6.79%</t>
+          <t>0.118M</t>
         </is>
       </c>
       <c r="E3127" t="inlineStr"/>
       <c r="F3127" t="inlineStr"/>
       <c r="G3127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3128">
       <c r="A3128" t="inlineStr">
         <is>
-          <t>2025-07-09 16:30:00+05:30</t>
+          <t>2025-07-09 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B3128" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJUL/04</t>
+          <t>EIA Gasoline Production ChangeJUL/04</t>
         </is>
       </c>
       <c r="C3128" t="inlineStr"/>
       <c r="D3128" t="inlineStr">
         <is>
-          <t>759.7</t>
+          <t>-0.491M</t>
         </is>
       </c>
       <c r="E3128" t="inlineStr"/>
@@ -87849,18 +87837,18 @@
     <row r="3129">
       <c r="A3129" t="inlineStr">
         <is>
-          <t>2025-07-09 16:30:00+05:30</t>
+          <t>2025-07-09 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B3129" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJUL/04</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C3129" t="inlineStr"/>
       <c r="D3129" t="inlineStr">
         <is>
-          <t>257.5</t>
+          <t>4.185%</t>
         </is>
       </c>
       <c r="E3129" t="inlineStr"/>
@@ -87872,18 +87860,18 @@
     <row r="3130">
       <c r="A3130" t="inlineStr">
         <is>
-          <t>2025-07-09 16:30:00+05:30</t>
+          <t>2025-07-09 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B3130" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJUL/04</t>
+          <t>10-Year Note Auction</t>
         </is>
       </c>
       <c r="C3130" t="inlineStr"/>
       <c r="D3130" t="inlineStr">
         <is>
-          <t>165.3</t>
+          <t>4.421%</t>
         </is>
       </c>
       <c r="E3130" t="inlineStr"/>
@@ -87895,51 +87883,47 @@
     <row r="3131">
       <c r="A3131" t="inlineStr">
         <is>
-          <t>2025-07-09 16:30:00+05:30</t>
+          <t>2025-07-09 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B3131" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJUL/04</t>
+          <t>FOMC Minutes</t>
         </is>
       </c>
       <c r="C3131" t="inlineStr"/>
-      <c r="D3131" t="inlineStr">
-        <is>
-          <t>2.7%</t>
-        </is>
-      </c>
+      <c r="D3131" t="inlineStr"/>
       <c r="E3131" t="inlineStr"/>
       <c r="F3131" t="inlineStr"/>
       <c r="G3131" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3132">
       <c r="A3132" t="inlineStr">
         <is>
-          <t>2025-07-09 19:30:00+05:30</t>
+          <t>2025-07-10 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3132" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMMAY</t>
+          <t>Continuing Jobless ClaimsJUN/28</t>
         </is>
       </c>
       <c r="C3132" t="inlineStr"/>
       <c r="D3132" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>1964K</t>
         </is>
       </c>
       <c r="E3132" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>1980K</t>
         </is>
       </c>
       <c r="F3132" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>1967.0K</t>
         </is>
       </c>
       <c r="G3132" t="n">
@@ -87949,28 +87933,24 @@
     <row r="3133">
       <c r="A3133" t="inlineStr">
         <is>
-          <t>2025-07-09 19:30:00+05:30</t>
+          <t>2025-07-10 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3133" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMMAY</t>
+          <t>Jobless Claims 4-week AverageJUL/05</t>
         </is>
       </c>
       <c r="C3133" t="inlineStr"/>
       <c r="D3133" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E3133" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>241.5K</t>
+        </is>
+      </c>
+      <c r="E3133" t="inlineStr"/>
       <c r="F3133" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>243.0K</t>
         </is>
       </c>
       <c r="G3133" t="n">
@@ -87980,22 +87960,30 @@
     <row r="3134">
       <c r="A3134" t="inlineStr">
         <is>
-          <t>2025-07-09 20:00:00+05:30</t>
+          <t>2025-07-10 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3134" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJUL/04</t>
+          <t>Initial Jobless ClaimsJUL/05</t>
         </is>
       </c>
       <c r="C3134" t="inlineStr"/>
       <c r="D3134" t="inlineStr">
         <is>
-          <t>4.188M</t>
-        </is>
-      </c>
-      <c r="E3134" t="inlineStr"/>
-      <c r="F3134" t="inlineStr"/>
+          <t>233K</t>
+        </is>
+      </c>
+      <c r="E3134" t="inlineStr">
+        <is>
+          <t>235K</t>
+        </is>
+      </c>
+      <c r="F3134" t="inlineStr">
+        <is>
+          <t>245.0K</t>
+        </is>
+      </c>
       <c r="G3134" t="n">
         <v>2</v>
       </c>
@@ -88003,41 +87991,37 @@
     <row r="3135">
       <c r="A3135" t="inlineStr">
         <is>
-          <t>2025-07-09 20:00:00+05:30</t>
+          <t>2025-07-10 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B3135" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJUL/04</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C3135" t="inlineStr"/>
-      <c r="D3135" t="inlineStr">
-        <is>
-          <t>2.94M</t>
-        </is>
-      </c>
+      <c r="D3135" t="inlineStr"/>
       <c r="E3135" t="inlineStr"/>
       <c r="F3135" t="inlineStr"/>
       <c r="G3135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3136">
       <c r="A3136" t="inlineStr">
         <is>
-          <t>2025-07-09 20:00:00+05:30</t>
+          <t>2025-07-10 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B3136" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJUL/04</t>
+          <t>EIA Natural Gas Stocks ChangeJUL/04</t>
         </is>
       </c>
       <c r="C3136" t="inlineStr"/>
       <c r="D3136" t="inlineStr">
         <is>
-          <t>-1.493M</t>
+          <t>55Bcf</t>
         </is>
       </c>
       <c r="E3136" t="inlineStr"/>
@@ -88049,18 +88033,18 @@
     <row r="3137">
       <c r="A3137" t="inlineStr">
         <is>
-          <t>2025-07-09 20:00:00+05:30</t>
+          <t>2025-07-10 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B3137" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJUL/04</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C3137" t="inlineStr"/>
       <c r="D3137" t="inlineStr">
         <is>
-          <t>0.245M</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="E3137" t="inlineStr"/>
@@ -88072,18 +88056,18 @@
     <row r="3138">
       <c r="A3138" t="inlineStr">
         <is>
-          <t>2025-07-09 20:00:00+05:30</t>
+          <t>2025-07-10 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B3138" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJUL/04</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C3138" t="inlineStr"/>
       <c r="D3138" t="inlineStr">
         <is>
-          <t>-1.71M</t>
+          <t>4.300%</t>
         </is>
       </c>
       <c r="E3138" t="inlineStr"/>
@@ -88095,18 +88079,18 @@
     <row r="3139">
       <c r="A3139" t="inlineStr">
         <is>
-          <t>2025-07-09 20:00:00+05:30</t>
+          <t>2025-07-10 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B3139" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJUL/04</t>
+          <t>30-Year Mortgage RateJUL/10</t>
         </is>
       </c>
       <c r="C3139" t="inlineStr"/>
       <c r="D3139" t="inlineStr">
         <is>
-          <t>-0.202M</t>
+          <t>6.67%</t>
         </is>
       </c>
       <c r="E3139" t="inlineStr"/>
@@ -88118,18 +88102,18 @@
     <row r="3140">
       <c r="A3140" t="inlineStr">
         <is>
-          <t>2025-07-09 20:00:00+05:30</t>
+          <t>2025-07-10 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B3140" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJUL/04</t>
+          <t>15-Year Mortgage RateJUL/10</t>
         </is>
       </c>
       <c r="C3140" t="inlineStr"/>
       <c r="D3140" t="inlineStr">
         <is>
-          <t>0.118M</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="E3140" t="inlineStr"/>
@@ -88141,21 +88125,21 @@
     <row r="3141">
       <c r="A3141" t="inlineStr">
         <is>
-          <t>2025-07-09 20:00:00+05:30</t>
+          <t>2025-07-10 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B3141" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases Bill 0 to 1 yrs</t>
+          <t>30-Year Bond Auction</t>
         </is>
       </c>
       <c r="C3141" t="inlineStr"/>
-      <c r="D3141" t="inlineStr"/>
-      <c r="E3141" t="inlineStr">
-        <is>
-          <t>$75 million</t>
-        </is>
-      </c>
+      <c r="D3141" t="inlineStr">
+        <is>
+          <t>4.844%</t>
+        </is>
+      </c>
+      <c r="E3141" t="inlineStr"/>
       <c r="F3141" t="inlineStr"/>
       <c r="G3141" t="n">
         <v>3</v>
@@ -88164,43 +88148,35 @@
     <row r="3142">
       <c r="A3142" t="inlineStr">
         <is>
-          <t>2025-07-09 20:00:00+05:30</t>
+          <t>2025-07-10 22:45:00+05:30</t>
         </is>
       </c>
       <c r="B3142" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJUL/04</t>
+          <t>Fed Waller Speech</t>
         </is>
       </c>
       <c r="C3142" t="inlineStr"/>
-      <c r="D3142" t="inlineStr">
-        <is>
-          <t>0.245M</t>
-        </is>
-      </c>
+      <c r="D3142" t="inlineStr"/>
       <c r="E3142" t="inlineStr"/>
       <c r="F3142" t="inlineStr"/>
       <c r="G3142" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3143">
       <c r="A3143" t="inlineStr">
         <is>
-          <t>2025-07-09 20:00:00+05:30</t>
+          <t>2025-07-11 00:00:00+05:30</t>
         </is>
       </c>
       <c r="B3143" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJUL/04</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C3143" t="inlineStr"/>
-      <c r="D3143" t="inlineStr">
-        <is>
-          <t>3.845M</t>
-        </is>
-      </c>
+      <c r="D3143" t="inlineStr"/>
       <c r="E3143" t="inlineStr"/>
       <c r="F3143" t="inlineStr"/>
       <c r="G3143" t="n">
@@ -88210,20 +88186,16 @@
     <row r="3144">
       <c r="A3144" t="inlineStr">
         <is>
-          <t>2025-07-09 20:00:00+05:30</t>
+          <t>2025-07-11 02:00:00+05:30</t>
         </is>
       </c>
       <c r="B3144" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJUL/04</t>
+          <t>Fed Balance SheetJUL/09</t>
         </is>
       </c>
       <c r="C3144" t="inlineStr"/>
-      <c r="D3144" t="inlineStr">
-        <is>
-          <t>-0.491M</t>
-        </is>
-      </c>
+      <c r="D3144" t="inlineStr"/>
       <c r="E3144" t="inlineStr"/>
       <c r="F3144" t="inlineStr"/>
       <c r="G3144" t="n">
@@ -88233,41 +88205,37 @@
     <row r="3145">
       <c r="A3145" t="inlineStr">
         <is>
-          <t>2025-07-09 20:00:00+05:30</t>
+          <t>2025-07-11 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B3145" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJUL/04</t>
+          <t>WASDE Report</t>
         </is>
       </c>
       <c r="C3145" t="inlineStr"/>
-      <c r="D3145" t="inlineStr">
-        <is>
-          <t>4.188M</t>
-        </is>
-      </c>
+      <c r="D3145" t="inlineStr"/>
       <c r="E3145" t="inlineStr"/>
       <c r="F3145" t="inlineStr"/>
       <c r="G3145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3146">
       <c r="A3146" t="inlineStr">
         <is>
-          <t>2025-07-09 20:00:00+05:30</t>
+          <t>2025-07-11 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B3146" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJUL/04</t>
+          <t>Baker Hughes Oil Rig CountJUL/11</t>
         </is>
       </c>
       <c r="C3146" t="inlineStr"/>
       <c r="D3146" t="inlineStr">
         <is>
-          <t>2.94M</t>
+          <t>425</t>
         </is>
       </c>
       <c r="E3146" t="inlineStr"/>
@@ -88279,66 +88247,70 @@
     <row r="3147">
       <c r="A3147" t="inlineStr">
         <is>
-          <t>2025-07-09 20:00:00+05:30</t>
+          <t>2025-07-11 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B3147" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJUL/04</t>
+          <t>Baker Hughes Total Rigs CountJUL/11</t>
         </is>
       </c>
       <c r="C3147" t="inlineStr"/>
       <c r="D3147" t="inlineStr">
         <is>
-          <t>3.845M</t>
+          <t>539</t>
         </is>
       </c>
       <c r="E3147" t="inlineStr"/>
       <c r="F3147" t="inlineStr"/>
       <c r="G3147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3148">
       <c r="A3148" t="inlineStr">
         <is>
-          <t>2025-07-09 20:00:00+05:30</t>
+          <t>2025-07-11 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B3148" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJUL/04</t>
+          <t>Monthly Budget StatementJUN</t>
         </is>
       </c>
       <c r="C3148" t="inlineStr"/>
       <c r="D3148" t="inlineStr">
         <is>
-          <t>-1.493M</t>
-        </is>
-      </c>
-      <c r="E3148" t="inlineStr"/>
-      <c r="F3148" t="inlineStr"/>
+          <t>$-316B</t>
+        </is>
+      </c>
+      <c r="E3148" t="inlineStr">
+        <is>
+          <t>$-60B</t>
+        </is>
+      </c>
+      <c r="F3148" t="inlineStr">
+        <is>
+          <t>$-350.0B</t>
+        </is>
+      </c>
       <c r="G3148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3149">
       <c r="A3149" t="inlineStr">
         <is>
-          <t>2025-07-09 20:00:00+05:30</t>
+          <t>2025-07-14 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B3149" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJUL/04</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C3149" t="inlineStr"/>
-      <c r="D3149" t="inlineStr">
-        <is>
-          <t>-1.71M</t>
-        </is>
-      </c>
+      <c r="D3149" t="inlineStr"/>
       <c r="E3149" t="inlineStr"/>
       <c r="F3149" t="inlineStr"/>
       <c r="G3149" t="n">
@@ -88348,21 +88320,17 @@
     <row r="3150">
       <c r="A3150" t="inlineStr">
         <is>
-          <t>2025-07-09 20:00:00+05:30</t>
+          <t>2025-07-14 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B3150" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases Bill 0 to 1 yrs</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C3150" t="inlineStr"/>
       <c r="D3150" t="inlineStr"/>
-      <c r="E3150" t="inlineStr">
-        <is>
-          <t>$75 million</t>
-        </is>
-      </c>
+      <c r="E3150" t="inlineStr"/>
       <c r="F3150" t="inlineStr"/>
       <c r="G3150" t="n">
         <v>3</v>
@@ -88371,173 +88339,197 @@
     <row r="3151">
       <c r="A3151" t="inlineStr">
         <is>
-          <t>2025-07-09 20:00:00+05:30</t>
+          <t>2025-07-15 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3151" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJUL/04</t>
+          <t>Core Inflation Rate MoMJUN</t>
         </is>
       </c>
       <c r="C3151" t="inlineStr"/>
       <c r="D3151" t="inlineStr">
         <is>
-          <t>-0.202M</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E3151" t="inlineStr"/>
-      <c r="F3151" t="inlineStr"/>
+      <c r="F3151" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="G3151" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3152">
       <c r="A3152" t="inlineStr">
         <is>
-          <t>2025-07-09 20:00:00+05:30</t>
+          <t>2025-07-15 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3152" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJUL/04</t>
+          <t>Core Inflation Rate YoYJUN</t>
         </is>
       </c>
       <c r="C3152" t="inlineStr"/>
       <c r="D3152" t="inlineStr">
         <is>
-          <t>0.118M</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E3152" t="inlineStr"/>
-      <c r="F3152" t="inlineStr"/>
+      <c r="F3152" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
       <c r="G3152" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3153">
       <c r="A3153" t="inlineStr">
         <is>
-          <t>2025-07-09 20:00:00+05:30</t>
+          <t>2025-07-15 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3153" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJUL/04</t>
+          <t>CPI s.aJUN</t>
         </is>
       </c>
       <c r="C3153" t="inlineStr"/>
       <c r="D3153" t="inlineStr">
         <is>
-          <t>-0.491M</t>
+          <t>320.580</t>
         </is>
       </c>
       <c r="E3153" t="inlineStr"/>
-      <c r="F3153" t="inlineStr"/>
+      <c r="F3153" t="inlineStr">
+        <is>
+          <t>321.2</t>
+        </is>
+      </c>
       <c r="G3153" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3154">
       <c r="A3154" t="inlineStr">
         <is>
-          <t>2025-07-09 21:00:00+05:30</t>
+          <t>2025-07-15 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3154" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>Inflation Rate YoYJUN</t>
         </is>
       </c>
       <c r="C3154" t="inlineStr"/>
       <c r="D3154" t="inlineStr">
         <is>
-          <t>4.185%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="E3154" t="inlineStr"/>
-      <c r="F3154" t="inlineStr"/>
+      <c r="F3154" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="G3154" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3155">
       <c r="A3155" t="inlineStr">
         <is>
-          <t>2025-07-09 21:00:00+05:30</t>
+          <t>2025-07-15 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3155" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>CPIJUN</t>
         </is>
       </c>
       <c r="C3155" t="inlineStr"/>
       <c r="D3155" t="inlineStr">
         <is>
-          <t>4.185%</t>
+          <t>321.465</t>
         </is>
       </c>
       <c r="E3155" t="inlineStr"/>
-      <c r="F3155" t="inlineStr"/>
+      <c r="F3155" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
       <c r="G3155" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3156">
       <c r="A3156" t="inlineStr">
         <is>
-          <t>2025-07-09 22:30:00+05:30</t>
+          <t>2025-07-15 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3156" t="inlineStr">
         <is>
-          <t>10-Year Note Auction</t>
+          <t>Inflation Rate MoMJUN</t>
         </is>
       </c>
       <c r="C3156" t="inlineStr"/>
       <c r="D3156" t="inlineStr">
         <is>
-          <t>4.421%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E3156" t="inlineStr"/>
-      <c r="F3156" t="inlineStr"/>
+      <c r="F3156" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="G3156" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3157">
       <c r="A3157" t="inlineStr">
         <is>
-          <t>2025-07-09 22:30:00+05:30</t>
+          <t>2025-07-15 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3157" t="inlineStr">
         <is>
-          <t>10-Year Note Auction</t>
+          <t>NY Empire State Manufacturing IndexJUL</t>
         </is>
       </c>
       <c r="C3157" t="inlineStr"/>
       <c r="D3157" t="inlineStr">
         <is>
-          <t>4.421%</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="E3157" t="inlineStr"/>
       <c r="F3157" t="inlineStr"/>
       <c r="G3157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3158">
       <c r="A3158" t="inlineStr">
         <is>
-          <t>2025-07-09 23:30:00+05:30</t>
+          <t>2025-07-15 18:25:00+05:30</t>
         </is>
       </c>
       <c r="B3158" t="inlineStr">
         <is>
-          <t>FOMC Minutes</t>
+          <t>Redbook YoYJUL/12</t>
         </is>
       </c>
       <c r="C3158" t="inlineStr"/>
@@ -88545,18 +88537,18 @@
       <c r="E3158" t="inlineStr"/>
       <c r="F3158" t="inlineStr"/>
       <c r="G3158" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3159">
       <c r="A3159" t="inlineStr">
         <is>
-          <t>2025-07-09 23:30:00+05:30</t>
+          <t>2025-07-15 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B3159" t="inlineStr">
         <is>
-          <t>FOMC Minutes</t>
+          <t>NOPA Crush Report</t>
         </is>
       </c>
       <c r="C3159" t="inlineStr"/>
@@ -88564,94 +88556,62 @@
       <c r="E3159" t="inlineStr"/>
       <c r="F3159" t="inlineStr"/>
       <c r="G3159" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3160">
       <c r="A3160" t="inlineStr">
         <is>
-          <t>2025-07-10 18:00:00+05:30</t>
+          <t>2025-07-16 02:00:00+05:30</t>
         </is>
       </c>
       <c r="B3160" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJUN/28</t>
+          <t>API Crude Oil Stock ChangeJUL/11</t>
         </is>
       </c>
       <c r="C3160" t="inlineStr"/>
-      <c r="D3160" t="inlineStr">
-        <is>
-          <t>1964K</t>
-        </is>
-      </c>
-      <c r="E3160" t="inlineStr">
-        <is>
-          <t>1980K</t>
-        </is>
-      </c>
-      <c r="F3160" t="inlineStr">
-        <is>
-          <t>1967.0K</t>
-        </is>
-      </c>
+      <c r="D3160" t="inlineStr"/>
+      <c r="E3160" t="inlineStr"/>
+      <c r="F3160" t="inlineStr"/>
       <c r="G3160" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3161">
       <c r="A3161" t="inlineStr">
         <is>
-          <t>2025-07-10 18:00:00+05:30</t>
+          <t>2025-07-16 16:30:00+05:30</t>
         </is>
       </c>
       <c r="B3161" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJUN/28</t>
+          <t>MBA 30-Year Mortgage RateJUL/11</t>
         </is>
       </c>
       <c r="C3161" t="inlineStr"/>
-      <c r="D3161" t="inlineStr">
-        <is>
-          <t>1964K</t>
-        </is>
-      </c>
-      <c r="E3161" t="inlineStr">
-        <is>
-          <t>1980K</t>
-        </is>
-      </c>
-      <c r="F3161" t="inlineStr">
-        <is>
-          <t>1967.0K</t>
-        </is>
-      </c>
+      <c r="D3161" t="inlineStr"/>
+      <c r="E3161" t="inlineStr"/>
+      <c r="F3161" t="inlineStr"/>
       <c r="G3161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3162">
       <c r="A3162" t="inlineStr">
         <is>
-          <t>2025-07-10 18:00:00+05:30</t>
+          <t>2025-07-16 16:30:00+05:30</t>
         </is>
       </c>
       <c r="B3162" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJUL/05</t>
+          <t>MBA Mortgage ApplicationsJUL/11</t>
         </is>
       </c>
       <c r="C3162" t="inlineStr"/>
-      <c r="D3162" t="inlineStr">
-        <is>
-          <t>241.5K</t>
-        </is>
-      </c>
+      <c r="D3162" t="inlineStr"/>
       <c r="E3162" t="inlineStr"/>
-      <c r="F3162" t="inlineStr">
-        <is>
-          <t>243.0K</t>
-        </is>
-      </c>
+      <c r="F3162" t="inlineStr"/>
       <c r="G3162" t="n">
         <v>3</v>
       </c>
@@ -88659,26 +88619,18 @@
     <row r="3163">
       <c r="A3163" t="inlineStr">
         <is>
-          <t>2025-07-10 18:00:00+05:30</t>
+          <t>2025-07-16 16:30:00+05:30</t>
         </is>
       </c>
       <c r="B3163" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJUL/05</t>
+          <t>MBA Mortgage Market IndexJUL/11</t>
         </is>
       </c>
       <c r="C3163" t="inlineStr"/>
-      <c r="D3163" t="inlineStr">
-        <is>
-          <t>241.5K</t>
-        </is>
-      </c>
+      <c r="D3163" t="inlineStr"/>
       <c r="E3163" t="inlineStr"/>
-      <c r="F3163" t="inlineStr">
-        <is>
-          <t>243.0K</t>
-        </is>
-      </c>
+      <c r="F3163" t="inlineStr"/>
       <c r="G3163" t="n">
         <v>3</v>
       </c>
@@ -88686,122 +88638,118 @@
     <row r="3164">
       <c r="A3164" t="inlineStr">
         <is>
-          <t>2025-07-10 18:00:00+05:30</t>
+          <t>2025-07-16 16:30:00+05:30</t>
         </is>
       </c>
       <c r="B3164" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJUL/05</t>
+          <t>MBA Mortgage Refinance IndexJUL/11</t>
         </is>
       </c>
       <c r="C3164" t="inlineStr"/>
-      <c r="D3164" t="inlineStr">
-        <is>
-          <t>233K</t>
-        </is>
-      </c>
-      <c r="E3164" t="inlineStr">
-        <is>
-          <t>235K</t>
-        </is>
-      </c>
-      <c r="F3164" t="inlineStr">
-        <is>
-          <t>245.0K</t>
-        </is>
-      </c>
+      <c r="D3164" t="inlineStr"/>
+      <c r="E3164" t="inlineStr"/>
+      <c r="F3164" t="inlineStr"/>
       <c r="G3164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3165">
       <c r="A3165" t="inlineStr">
         <is>
-          <t>2025-07-10 18:00:00+05:30</t>
+          <t>2025-07-16 16:30:00+05:30</t>
         </is>
       </c>
       <c r="B3165" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJUL/05</t>
+          <t>MBA Purchase IndexJUL/11</t>
         </is>
       </c>
       <c r="C3165" t="inlineStr"/>
-      <c r="D3165" t="inlineStr">
-        <is>
-          <t>233K</t>
-        </is>
-      </c>
-      <c r="E3165" t="inlineStr">
-        <is>
-          <t>235K</t>
-        </is>
-      </c>
-      <c r="F3165" t="inlineStr">
-        <is>
-          <t>245.0K</t>
-        </is>
-      </c>
+      <c r="D3165" t="inlineStr"/>
+      <c r="E3165" t="inlineStr"/>
+      <c r="F3165" t="inlineStr"/>
       <c r="G3165" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3166">
       <c r="A3166" t="inlineStr">
         <is>
-          <t>2025-07-10 19:30:00+05:30</t>
+          <t>2025-07-16 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3166" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>PPI YoYJUN</t>
         </is>
       </c>
       <c r="C3166" t="inlineStr"/>
-      <c r="D3166" t="inlineStr"/>
+      <c r="D3166" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E3166" t="inlineStr"/>
-      <c r="F3166" t="inlineStr"/>
+      <c r="F3166" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="G3166" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3167">
       <c r="A3167" t="inlineStr">
         <is>
-          <t>2025-07-10 19:30:00+05:30</t>
+          <t>2025-07-16 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3167" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>PPI Ex Food, Energy and Trade YoYJUN</t>
         </is>
       </c>
       <c r="C3167" t="inlineStr"/>
-      <c r="D3167" t="inlineStr"/>
+      <c r="D3167" t="inlineStr">
+        <is>
+          <t>2.7%</t>
+        </is>
+      </c>
       <c r="E3167" t="inlineStr"/>
-      <c r="F3167" t="inlineStr"/>
+      <c r="F3167" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="G3167" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3168">
       <c r="A3168" t="inlineStr">
         <is>
-          <t>2025-07-10 20:00:00+05:30</t>
+          <t>2025-07-16 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3168" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeJUL/04</t>
+          <t>Core PPI YoYJUN</t>
         </is>
       </c>
       <c r="C3168" t="inlineStr"/>
       <c r="D3168" t="inlineStr">
         <is>
-          <t>55Bcf</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E3168" t="inlineStr"/>
-      <c r="F3168" t="inlineStr"/>
+      <c r="F3168" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="G3168" t="n">
         <v>3</v>
       </c>
@@ -88809,22 +88757,26 @@
     <row r="3169">
       <c r="A3169" t="inlineStr">
         <is>
-          <t>2025-07-10 20:00:00+05:30</t>
+          <t>2025-07-16 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3169" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeJUL/04</t>
+          <t>PPI Ex Food, Energy and Trade MoMJUN</t>
         </is>
       </c>
       <c r="C3169" t="inlineStr"/>
       <c r="D3169" t="inlineStr">
         <is>
-          <t>55Bcf</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E3169" t="inlineStr"/>
-      <c r="F3169" t="inlineStr"/>
+      <c r="F3169" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="G3169" t="n">
         <v>3</v>
       </c>
@@ -88832,68 +88784,80 @@
     <row r="3170">
       <c r="A3170" t="inlineStr">
         <is>
-          <t>2025-07-10 21:00:00+05:30</t>
+          <t>2025-07-16 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3170" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>Core PPI MoMJUN</t>
         </is>
       </c>
       <c r="C3170" t="inlineStr"/>
       <c r="D3170" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E3170" t="inlineStr"/>
-      <c r="F3170" t="inlineStr"/>
+      <c r="F3170" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="G3170" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3171">
       <c r="A3171" t="inlineStr">
         <is>
-          <t>2025-07-10 21:00:00+05:30</t>
+          <t>2025-07-16 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3171" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>PPI MoMJUN</t>
         </is>
       </c>
       <c r="C3171" t="inlineStr"/>
       <c r="D3171" t="inlineStr">
         <is>
-          <t>4.300%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E3171" t="inlineStr"/>
-      <c r="F3171" t="inlineStr"/>
+      <c r="F3171" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="G3171" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3172">
       <c r="A3172" t="inlineStr">
         <is>
-          <t>2025-07-10 21:00:00+05:30</t>
+          <t>2025-07-16 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3172" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>PPIJUN</t>
         </is>
       </c>
       <c r="C3172" t="inlineStr"/>
       <c r="D3172" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>148.072</t>
         </is>
       </c>
       <c r="E3172" t="inlineStr"/>
-      <c r="F3172" t="inlineStr"/>
+      <c r="F3172" t="inlineStr">
+        <is>
+          <t>148.9</t>
+        </is>
+      </c>
       <c r="G3172" t="n">
         <v>3</v>
       </c>
@@ -88901,22 +88865,26 @@
     <row r="3173">
       <c r="A3173" t="inlineStr">
         <is>
-          <t>2025-07-10 21:00:00+05:30</t>
+          <t>2025-07-16 18:45:00+05:30</t>
         </is>
       </c>
       <c r="B3173" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>Manufacturing Production YoYJUN</t>
         </is>
       </c>
       <c r="C3173" t="inlineStr"/>
       <c r="D3173" t="inlineStr">
         <is>
-          <t>4.300%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E3173" t="inlineStr"/>
-      <c r="F3173" t="inlineStr"/>
+      <c r="F3173" t="inlineStr">
+        <is>
+          <t>1.1%</t>
+        </is>
+      </c>
       <c r="G3173" t="n">
         <v>3</v>
       </c>
@@ -88924,45 +88892,45 @@
     <row r="3174">
       <c r="A3174" t="inlineStr">
         <is>
-          <t>2025-07-10 21:30:00+05:30</t>
+          <t>2025-07-16 18:45:00+05:30</t>
         </is>
       </c>
       <c r="B3174" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJUL/10</t>
+          <t>Fed Hammack Speech</t>
         </is>
       </c>
       <c r="C3174" t="inlineStr"/>
-      <c r="D3174" t="inlineStr">
-        <is>
-          <t>6.67%</t>
-        </is>
-      </c>
+      <c r="D3174" t="inlineStr"/>
       <c r="E3174" t="inlineStr"/>
       <c r="F3174" t="inlineStr"/>
       <c r="G3174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3175">
       <c r="A3175" t="inlineStr">
         <is>
-          <t>2025-07-10 21:30:00+05:30</t>
+          <t>2025-07-16 18:45:00+05:30</t>
         </is>
       </c>
       <c r="B3175" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJUL/10</t>
+          <t>Capacity UtilizationJUN</t>
         </is>
       </c>
       <c r="C3175" t="inlineStr"/>
       <c r="D3175" t="inlineStr">
         <is>
-          <t>6.67%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="E3175" t="inlineStr"/>
-      <c r="F3175" t="inlineStr"/>
+      <c r="F3175" t="inlineStr">
+        <is>
+          <t>77.4%</t>
+        </is>
+      </c>
       <c r="G3175" t="n">
         <v>3</v>
       </c>
@@ -88970,18 +88938,18 @@
     <row r="3176">
       <c r="A3176" t="inlineStr">
         <is>
-          <t>2025-07-10 21:30:00+05:30</t>
+          <t>2025-07-16 18:45:00+05:30</t>
         </is>
       </c>
       <c r="B3176" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJUL/10</t>
+          <t>Manufacturing Production MoMJUN</t>
         </is>
       </c>
       <c r="C3176" t="inlineStr"/>
       <c r="D3176" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E3176" t="inlineStr"/>
@@ -88993,45 +88961,53 @@
     <row r="3177">
       <c r="A3177" t="inlineStr">
         <is>
-          <t>2025-07-10 21:30:00+05:30</t>
+          <t>2025-07-16 18:45:00+05:30</t>
         </is>
       </c>
       <c r="B3177" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJUL/10</t>
+          <t>Industrial Production MoMJUN</t>
         </is>
       </c>
       <c r="C3177" t="inlineStr"/>
       <c r="D3177" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="E3177" t="inlineStr"/>
-      <c r="F3177" t="inlineStr"/>
+      <c r="F3177" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="G3177" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3178">
       <c r="A3178" t="inlineStr">
         <is>
-          <t>2025-07-10 22:30:00+05:30</t>
+          <t>2025-07-16 18:45:00+05:30</t>
         </is>
       </c>
       <c r="B3178" t="inlineStr">
         <is>
-          <t>30-Year Bond Auction</t>
+          <t>Industrial Production YoYJUN</t>
         </is>
       </c>
       <c r="C3178" t="inlineStr"/>
       <c r="D3178" t="inlineStr">
         <is>
-          <t>4.844%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E3178" t="inlineStr"/>
-      <c r="F3178" t="inlineStr"/>
+      <c r="F3178" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
+      </c>
       <c r="G3178" t="n">
         <v>3</v>
       </c>
@@ -89039,20 +89015,16 @@
     <row r="3179">
       <c r="A3179" t="inlineStr">
         <is>
-          <t>2025-07-10 22:30:00+05:30</t>
+          <t>2025-07-16 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B3179" t="inlineStr">
         <is>
-          <t>30-Year Bond Auction</t>
+          <t>EIA Crude Oil Imports ChangeJUL/11</t>
         </is>
       </c>
       <c r="C3179" t="inlineStr"/>
-      <c r="D3179" t="inlineStr">
-        <is>
-          <t>4.844%</t>
-        </is>
-      </c>
+      <c r="D3179" t="inlineStr"/>
       <c r="E3179" t="inlineStr"/>
       <c r="F3179" t="inlineStr"/>
       <c r="G3179" t="n">
@@ -89062,12 +89034,12 @@
     <row r="3180">
       <c r="A3180" t="inlineStr">
         <is>
-          <t>2025-07-10 22:45:00+05:30</t>
+          <t>2025-07-16 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B3180" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
+          <t>EIA Gasoline Stocks ChangeJUL/11</t>
         </is>
       </c>
       <c r="C3180" t="inlineStr"/>
@@ -89081,12 +89053,12 @@
     <row r="3181">
       <c r="A3181" t="inlineStr">
         <is>
-          <t>2025-07-10 22:45:00+05:30</t>
+          <t>2025-07-16 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B3181" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
+          <t>EIA Distillate Fuel Production ChangeJUL/11</t>
         </is>
       </c>
       <c r="C3181" t="inlineStr"/>
@@ -89094,18 +89066,18 @@
       <c r="E3181" t="inlineStr"/>
       <c r="F3181" t="inlineStr"/>
       <c r="G3181" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3182">
       <c r="A3182" t="inlineStr">
         <is>
-          <t>2025-07-11 00:00:00+05:30</t>
+          <t>2025-07-16 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B3182" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>EIA Refinery Crude Runs ChangeJUL/11</t>
         </is>
       </c>
       <c r="C3182" t="inlineStr"/>
@@ -89113,18 +89085,18 @@
       <c r="E3182" t="inlineStr"/>
       <c r="F3182" t="inlineStr"/>
       <c r="G3182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3183">
       <c r="A3183" t="inlineStr">
         <is>
-          <t>2025-07-11 00:00:00+05:30</t>
+          <t>2025-07-16 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B3183" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>EIA Distillate Stocks ChangeJUL/11</t>
         </is>
       </c>
       <c r="C3183" t="inlineStr"/>
@@ -89132,26 +89104,22 @@
       <c r="E3183" t="inlineStr"/>
       <c r="F3183" t="inlineStr"/>
       <c r="G3183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3184">
       <c r="A3184" t="inlineStr">
         <is>
-          <t>2025-07-11 02:00:00+05:30</t>
+          <t>2025-07-16 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B3184" t="inlineStr">
         <is>
-          <t>Fed Balance SheetJUL/09</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJUL/11</t>
         </is>
       </c>
       <c r="C3184" t="inlineStr"/>
-      <c r="D3184" t="inlineStr">
-        <is>
-          <t>$6.66T</t>
-        </is>
-      </c>
+      <c r="D3184" t="inlineStr"/>
       <c r="E3184" t="inlineStr"/>
       <c r="F3184" t="inlineStr"/>
       <c r="G3184" t="n">
@@ -89161,12 +89129,12 @@
     <row r="3185">
       <c r="A3185" t="inlineStr">
         <is>
-          <t>2025-07-11 02:00:00+05:30</t>
+          <t>2025-07-16 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B3185" t="inlineStr">
         <is>
-          <t>Fed Balance SheetJUL/09</t>
+          <t>EIA Crude Oil Stocks ChangeJUL/11</t>
         </is>
       </c>
       <c r="C3185" t="inlineStr"/>
@@ -89174,18 +89142,18 @@
       <c r="E3185" t="inlineStr"/>
       <c r="F3185" t="inlineStr"/>
       <c r="G3185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3186">
       <c r="A3186" t="inlineStr">
         <is>
-          <t>2025-07-11 21:30:00+05:30</t>
+          <t>2025-07-16 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B3186" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
+          <t>EIA Gasoline Production ChangeJUL/11</t>
         </is>
       </c>
       <c r="C3186" t="inlineStr"/>
@@ -89199,12 +89167,12 @@
     <row r="3187">
       <c r="A3187" t="inlineStr">
         <is>
-          <t>2025-07-11 21:30:00+05:30</t>
+          <t>2025-07-16 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B3187" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
+          <t>EIA Heating Oil Stocks ChangeJUL/11</t>
         </is>
       </c>
       <c r="C3187" t="inlineStr"/>
@@ -89218,20 +89186,16 @@
     <row r="3188">
       <c r="A3188" t="inlineStr">
         <is>
-          <t>2025-07-11 22:30:00+05:30</t>
+          <t>2025-07-16 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B3188" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJUL/11</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C3188" t="inlineStr"/>
-      <c r="D3188" t="inlineStr">
-        <is>
-          <t>425</t>
-        </is>
-      </c>
+      <c r="D3188" t="inlineStr"/>
       <c r="E3188" t="inlineStr"/>
       <c r="F3188" t="inlineStr"/>
       <c r="G3188" t="n">
@@ -89241,20 +89205,16 @@
     <row r="3189">
       <c r="A3189" t="inlineStr">
         <is>
-          <t>2025-07-11 22:30:00+05:30</t>
+          <t>2025-07-16 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B3189" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJUL/11</t>
+          <t>Fed Beige Book</t>
         </is>
       </c>
       <c r="C3189" t="inlineStr"/>
-      <c r="D3189" t="inlineStr">
-        <is>
-          <t>425</t>
-        </is>
-      </c>
+      <c r="D3189" t="inlineStr"/>
       <c r="E3189" t="inlineStr"/>
       <c r="F3189" t="inlineStr"/>
       <c r="G3189" t="n">
@@ -89264,126 +89224,110 @@
     <row r="3190">
       <c r="A3190" t="inlineStr">
         <is>
-          <t>2025-07-11 22:30:00+05:30</t>
+          <t>2025-07-17 04:00:00+05:30</t>
         </is>
       </c>
       <c r="B3190" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJUL/11</t>
+          <t>Fed Williams Speech</t>
         </is>
       </c>
       <c r="C3190" t="inlineStr"/>
-      <c r="D3190" t="inlineStr">
-        <is>
-          <t>539</t>
-        </is>
-      </c>
+      <c r="D3190" t="inlineStr"/>
       <c r="E3190" t="inlineStr"/>
       <c r="F3190" t="inlineStr"/>
       <c r="G3190" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3191">
       <c r="A3191" t="inlineStr">
         <is>
-          <t>2025-07-11 22:30:00+05:30</t>
+          <t>2025-07-17 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3191" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJUL/11</t>
+          <t>Retail Sales Ex Autos MoMJUN</t>
         </is>
       </c>
       <c r="C3191" t="inlineStr"/>
       <c r="D3191" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="E3191" t="inlineStr"/>
-      <c r="F3191" t="inlineStr"/>
+      <c r="F3191" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="G3191" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3192">
       <c r="A3192" t="inlineStr">
         <is>
-          <t>2025-07-11 23:30:00+05:30</t>
+          <t>2025-07-17 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3192" t="inlineStr">
         <is>
-          <t>Monthly Budget StatementJUN</t>
+          <t>Philly Fed Business ConditionsJUL</t>
         </is>
       </c>
       <c r="C3192" t="inlineStr"/>
-      <c r="D3192" t="inlineStr">
-        <is>
-          <t>$-316B</t>
-        </is>
-      </c>
-      <c r="E3192" t="inlineStr">
-        <is>
-          <t>$-60B</t>
-        </is>
-      </c>
-      <c r="F3192" t="inlineStr">
-        <is>
-          <t>$-350.0B</t>
-        </is>
-      </c>
+      <c r="D3192" t="inlineStr"/>
+      <c r="E3192" t="inlineStr"/>
+      <c r="F3192" t="inlineStr"/>
       <c r="G3192" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3193">
       <c r="A3193" t="inlineStr">
         <is>
-          <t>2025-07-11 23:30:00+05:30</t>
+          <t>2025-07-17 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3193" t="inlineStr">
         <is>
-          <t>Monthly Budget StatementJUN</t>
+          <t>Export Prices YoYJUN</t>
         </is>
       </c>
       <c r="C3193" t="inlineStr"/>
       <c r="D3193" t="inlineStr">
         <is>
-          <t>$-316B</t>
-        </is>
-      </c>
-      <c r="E3193" t="inlineStr">
-        <is>
-          <t>$-60B</t>
-        </is>
-      </c>
-      <c r="F3193" t="inlineStr">
-        <is>
-          <t>$-350.0B</t>
-        </is>
-      </c>
+          <t>1.7%</t>
+        </is>
+      </c>
+      <c r="E3193" t="inlineStr"/>
+      <c r="F3193" t="inlineStr"/>
       <c r="G3193" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3194">
       <c r="A3194" t="inlineStr">
         <is>
-          <t>2025-07-14 21:00:00+05:30</t>
+          <t>2025-07-17 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3194" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>Continuing Jobless ClaimsJUL/05</t>
         </is>
       </c>
       <c r="C3194" t="inlineStr"/>
       <c r="D3194" t="inlineStr"/>
       <c r="E3194" t="inlineStr"/>
-      <c r="F3194" t="inlineStr"/>
+      <c r="F3194" t="inlineStr">
+        <is>
+          <t>1970.0K</t>
+        </is>
+      </c>
       <c r="G3194" t="n">
         <v>3</v>
       </c>
@@ -89391,31 +89335,39 @@
     <row r="3195">
       <c r="A3195" t="inlineStr">
         <is>
-          <t>2025-07-14 21:00:00+05:30</t>
+          <t>2025-07-17 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3195" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>Retail Sales MoMJUN</t>
         </is>
       </c>
       <c r="C3195" t="inlineStr"/>
-      <c r="D3195" t="inlineStr"/>
+      <c r="D3195" t="inlineStr">
+        <is>
+          <t>-0.9%</t>
+        </is>
+      </c>
       <c r="E3195" t="inlineStr"/>
-      <c r="F3195" t="inlineStr"/>
+      <c r="F3195" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="G3195" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3196">
       <c r="A3196" t="inlineStr">
         <is>
-          <t>2025-07-14 21:00:00+05:30</t>
+          <t>2025-07-17 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3196" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>Initial Jobless ClaimsJUL/12</t>
         </is>
       </c>
       <c r="C3196" t="inlineStr"/>
@@ -89423,240 +89375,212 @@
       <c r="E3196" t="inlineStr"/>
       <c r="F3196" t="inlineStr"/>
       <c r="G3196" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3197">
       <c r="A3197" t="inlineStr">
         <is>
-          <t>2025-07-14 21:00:00+05:30</t>
+          <t>2025-07-17 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3197" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>Import Prices MoMJUN</t>
         </is>
       </c>
       <c r="C3197" t="inlineStr"/>
-      <c r="D3197" t="inlineStr"/>
+      <c r="D3197" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E3197" t="inlineStr"/>
       <c r="F3197" t="inlineStr"/>
       <c r="G3197" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3198">
       <c r="A3198" t="inlineStr">
         <is>
-          <t>2025-07-15 18:00:00+05:30</t>
+          <t>2025-07-17 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3198" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJUN</t>
+          <t>Jobless Claims 4-week AverageJUL/12</t>
         </is>
       </c>
       <c r="C3198" t="inlineStr"/>
-      <c r="D3198" t="inlineStr">
-        <is>
-          <t>2.4%</t>
-        </is>
-      </c>
+      <c r="D3198" t="inlineStr"/>
       <c r="E3198" t="inlineStr"/>
-      <c r="F3198" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+      <c r="F3198" t="inlineStr"/>
       <c r="G3198" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3199">
       <c r="A3199" t="inlineStr">
         <is>
-          <t>2025-07-15 18:00:00+05:30</t>
+          <t>2025-07-17 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3199" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJUN</t>
+          <t>Export Prices MoMJUN</t>
         </is>
       </c>
       <c r="C3199" t="inlineStr"/>
       <c r="D3199" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="E3199" t="inlineStr"/>
       <c r="F3199" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="G3199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3200">
       <c r="A3200" t="inlineStr">
         <is>
-          <t>2025-07-15 18:00:00+05:30</t>
+          <t>2025-07-17 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3200" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJUN</t>
+          <t>Philly Fed New OrdersJUL</t>
         </is>
       </c>
       <c r="C3200" t="inlineStr"/>
       <c r="D3200" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="E3200" t="inlineStr"/>
-      <c r="F3200" t="inlineStr">
-        <is>
-          <t>2.9%</t>
-        </is>
-      </c>
+      <c r="F3200" t="inlineStr"/>
       <c r="G3200" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3201">
       <c r="A3201" t="inlineStr">
         <is>
-          <t>2025-07-15 18:00:00+05:30</t>
+          <t>2025-07-17 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3201" t="inlineStr">
         <is>
-          <t>CPI s.aJUN</t>
+          <t>Philly Fed CAPEX IndexJUL</t>
         </is>
       </c>
       <c r="C3201" t="inlineStr"/>
       <c r="D3201" t="inlineStr">
         <is>
-          <t>320.580</t>
+          <t>14.50</t>
         </is>
       </c>
       <c r="E3201" t="inlineStr"/>
-      <c r="F3201" t="inlineStr">
-        <is>
-          <t>321.2</t>
-        </is>
-      </c>
+      <c r="F3201" t="inlineStr"/>
       <c r="G3201" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3202">
       <c r="A3202" t="inlineStr">
         <is>
-          <t>2025-07-15 18:00:00+05:30</t>
+          <t>2025-07-17 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3202" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJUN</t>
+          <t>Philadelphia Fed Manufacturing IndexJUL</t>
         </is>
       </c>
       <c r="C3202" t="inlineStr"/>
       <c r="D3202" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="E3202" t="inlineStr"/>
-      <c r="F3202" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="F3202" t="inlineStr"/>
       <c r="G3202" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3203">
       <c r="A3203" t="inlineStr">
         <is>
-          <t>2025-07-15 18:00:00+05:30</t>
+          <t>2025-07-17 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3203" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJUN</t>
+          <t>Import Prices YoYJUN</t>
         </is>
       </c>
       <c r="C3203" t="inlineStr"/>
-      <c r="D3203" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+      <c r="D3203" t="inlineStr"/>
       <c r="E3203" t="inlineStr"/>
       <c r="F3203" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G3203" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3204">
       <c r="A3204" t="inlineStr">
         <is>
-          <t>2025-07-15 18:00:00+05:30</t>
+          <t>2025-07-17 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3204" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJUN</t>
+          <t>Philly Fed EmploymentJUL</t>
         </is>
       </c>
       <c r="C3204" t="inlineStr"/>
       <c r="D3204" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-9.8</t>
         </is>
       </c>
       <c r="E3204" t="inlineStr"/>
-      <c r="F3204" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="F3204" t="inlineStr"/>
       <c r="G3204" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3205">
       <c r="A3205" t="inlineStr">
         <is>
-          <t>2025-07-15 18:00:00+05:30</t>
+          <t>2025-07-17 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3205" t="inlineStr">
         <is>
-          <t>CPIJUN</t>
+          <t>Retail Sales Control Group MoMJUN</t>
         </is>
       </c>
       <c r="C3205" t="inlineStr"/>
       <c r="D3205" t="inlineStr">
         <is>
-          <t>321.465</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E3205" t="inlineStr"/>
-      <c r="F3205" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
+      <c r="F3205" t="inlineStr"/>
       <c r="G3205" t="n">
         <v>2</v>
       </c>
@@ -89664,103 +89588,99 @@
     <row r="3206">
       <c r="A3206" t="inlineStr">
         <is>
-          <t>2025-07-15 18:00:00+05:30</t>
+          <t>2025-07-17 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3206" t="inlineStr">
         <is>
-          <t>CPI s.aJUN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJUN</t>
         </is>
       </c>
       <c r="C3206" t="inlineStr"/>
       <c r="D3206" t="inlineStr">
         <is>
-          <t>320.580</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E3206" t="inlineStr"/>
       <c r="F3206" t="inlineStr">
         <is>
-          <t>321.2</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G3206" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3207">
       <c r="A3207" t="inlineStr">
         <is>
-          <t>2025-07-15 18:00:00+05:30</t>
+          <t>2025-07-17 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3207" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJUL</t>
+          <t>Philly Fed Prices PaidJUL</t>
         </is>
       </c>
       <c r="C3207" t="inlineStr"/>
       <c r="D3207" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>41.40</t>
         </is>
       </c>
       <c r="E3207" t="inlineStr"/>
       <c r="F3207" t="inlineStr"/>
       <c r="G3207" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3208">
       <c r="A3208" t="inlineStr">
         <is>
-          <t>2025-07-15 18:00:00+05:30</t>
+          <t>2025-07-17 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B3208" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJUN</t>
+          <t>Retail Sales YoYJUN</t>
         </is>
       </c>
       <c r="C3208" t="inlineStr"/>
       <c r="D3208" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E3208" t="inlineStr"/>
       <c r="F3208" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G3208" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3209">
       <c r="A3209" t="inlineStr">
         <is>
-          <t>2025-07-15 18:00:00+05:30</t>
+          <t>2025-07-17 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B3209" t="inlineStr">
         <is>
-          <t>CPIJUN</t>
+          <t>NAHB Housing Market IndexJUL</t>
         </is>
       </c>
       <c r="C3209" t="inlineStr"/>
       <c r="D3209" t="inlineStr">
         <is>
-          <t>321.465</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E3209" t="inlineStr"/>
-      <c r="F3209" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
+      <c r="F3209" t="inlineStr"/>
       <c r="G3209" t="n">
         <v>2</v>
       </c>
@@ -89768,45 +89688,37 @@
     <row r="3210">
       <c r="A3210" t="inlineStr">
         <is>
-          <t>2025-07-15 18:00:00+05:30</t>
+          <t>2025-07-17 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B3210" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJUN</t>
+          <t>Retail Inventories Ex Autos MoMMAY</t>
         </is>
       </c>
       <c r="C3210" t="inlineStr"/>
-      <c r="D3210" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D3210" t="inlineStr"/>
       <c r="E3210" t="inlineStr"/>
-      <c r="F3210" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="F3210" t="inlineStr"/>
       <c r="G3210" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3211">
       <c r="A3211" t="inlineStr">
         <is>
-          <t>2025-07-15 18:00:00+05:30</t>
+          <t>2025-07-17 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B3211" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJUL</t>
+          <t>Business Inventories MoMMAY</t>
         </is>
       </c>
       <c r="C3211" t="inlineStr"/>
       <c r="D3211" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E3211" t="inlineStr"/>
@@ -89818,12 +89730,12 @@
     <row r="3212">
       <c r="A3212" t="inlineStr">
         <is>
-          <t>2025-07-15 18:25:00+05:30</t>
+          <t>2025-07-17 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B3212" t="inlineStr">
         <is>
-          <t>Redbook YoYJUL/12</t>
+          <t>EIA Natural Gas Stocks ChangeJUL/11</t>
         </is>
       </c>
       <c r="C3212" t="inlineStr"/>
@@ -89837,12 +89749,12 @@
     <row r="3213">
       <c r="A3213" t="inlineStr">
         <is>
-          <t>2025-07-15 18:25:00+05:30</t>
+          <t>2025-07-17 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B3213" t="inlineStr">
         <is>
-          <t>Redbook YoYJUL/12</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C3213" t="inlineStr"/>
@@ -89856,12 +89768,12 @@
     <row r="3214">
       <c r="A3214" t="inlineStr">
         <is>
-          <t>2025-07-15 21:30:00+05:30</t>
+          <t>2025-07-17 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B3214" t="inlineStr">
         <is>
-          <t>NOPA Crush Report</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C3214" t="inlineStr"/>
@@ -89875,12 +89787,12 @@
     <row r="3215">
       <c r="A3215" t="inlineStr">
         <is>
-          <t>2025-07-15 21:30:00+05:30</t>
+          <t>2025-07-17 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B3215" t="inlineStr">
         <is>
-          <t>NOPA Crush Report</t>
+          <t>15-Year Mortgage RateJUL/17</t>
         </is>
       </c>
       <c r="C3215" t="inlineStr"/>
@@ -89894,12 +89806,12 @@
     <row r="3216">
       <c r="A3216" t="inlineStr">
         <is>
-          <t>2025-07-16 02:00:00+05:30</t>
+          <t>2025-07-17 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B3216" t="inlineStr">
         <is>
-          <t>API Crude Oil Stock ChangeJUL/11</t>
+          <t>30-Year Mortgage RateJUL/17</t>
         </is>
       </c>
       <c r="C3216" t="inlineStr"/>
@@ -89907,41 +89819,49 @@
       <c r="E3216" t="inlineStr"/>
       <c r="F3216" t="inlineStr"/>
       <c r="G3216" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3217">
       <c r="A3217" t="inlineStr">
         <is>
-          <t>2025-07-16 02:00:00+05:30</t>
+          <t>2025-07-18 01:30:00+05:30</t>
         </is>
       </c>
       <c r="B3217" t="inlineStr">
         <is>
-          <t>API Crude Oil Stock ChangeJUL/11</t>
+          <t>Overall Net Capital FlowsMAY</t>
         </is>
       </c>
       <c r="C3217" t="inlineStr"/>
-      <c r="D3217" t="inlineStr"/>
+      <c r="D3217" t="inlineStr">
+        <is>
+          <t>$-14.2B</t>
+        </is>
+      </c>
       <c r="E3217" t="inlineStr"/>
       <c r="F3217" t="inlineStr"/>
       <c r="G3217" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3218">
       <c r="A3218" t="inlineStr">
         <is>
-          <t>2025-07-16 16:30:00+05:30</t>
+          <t>2025-07-18 01:30:00+05:30</t>
         </is>
       </c>
       <c r="B3218" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJUL/11</t>
+          <t>Net Long-term TIC FlowsMAY</t>
         </is>
       </c>
       <c r="C3218" t="inlineStr"/>
-      <c r="D3218" t="inlineStr"/>
+      <c r="D3218" t="inlineStr">
+        <is>
+          <t>$-7.8B</t>
+        </is>
+      </c>
       <c r="E3218" t="inlineStr"/>
       <c r="F3218" t="inlineStr"/>
       <c r="G3218" t="n">
@@ -89951,16 +89871,20 @@
     <row r="3219">
       <c r="A3219" t="inlineStr">
         <is>
-          <t>2025-07-16 16:30:00+05:30</t>
+          <t>2025-07-18 01:30:00+05:30</t>
         </is>
       </c>
       <c r="B3219" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJUL/11</t>
+          <t>Foreign Bond InvestmentMAY</t>
         </is>
       </c>
       <c r="C3219" t="inlineStr"/>
-      <c r="D3219" t="inlineStr"/>
+      <c r="D3219" t="inlineStr">
+        <is>
+          <t>$-40.8B</t>
+        </is>
+      </c>
       <c r="E3219" t="inlineStr"/>
       <c r="F3219" t="inlineStr"/>
       <c r="G3219" t="n">
@@ -89970,12 +89894,12 @@
     <row r="3220">
       <c r="A3220" t="inlineStr">
         <is>
-          <t>2025-07-16 16:30:00+05:30</t>
+          <t>2025-07-18 02:00:00+05:30</t>
         </is>
       </c>
       <c r="B3220" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJUL/11</t>
+          <t>Fed Balance SheetJUL/16</t>
         </is>
       </c>
       <c r="C3220" t="inlineStr"/>
@@ -89986,2613 +89910,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3221">
-      <c r="A3221" t="inlineStr">
-        <is>
-          <t>2025-07-16 16:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3221" t="inlineStr">
-        <is>
-          <t>MBA Mortgage Refinance IndexJUL/11</t>
-        </is>
-      </c>
-      <c r="C3221" t="inlineStr"/>
-      <c r="D3221" t="inlineStr"/>
-      <c r="E3221" t="inlineStr"/>
-      <c r="F3221" t="inlineStr"/>
-      <c r="G3221" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3222">
-      <c r="A3222" t="inlineStr">
-        <is>
-          <t>2025-07-16 16:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3222" t="inlineStr">
-        <is>
-          <t>MBA 30-Year Mortgage RateJUL/11</t>
-        </is>
-      </c>
-      <c r="C3222" t="inlineStr"/>
-      <c r="D3222" t="inlineStr"/>
-      <c r="E3222" t="inlineStr"/>
-      <c r="F3222" t="inlineStr"/>
-      <c r="G3222" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3223">
-      <c r="A3223" t="inlineStr">
-        <is>
-          <t>2025-07-16 16:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3223" t="inlineStr">
-        <is>
-          <t>MBA Mortgage ApplicationsJUL/11</t>
-        </is>
-      </c>
-      <c r="C3223" t="inlineStr"/>
-      <c r="D3223" t="inlineStr"/>
-      <c r="E3223" t="inlineStr"/>
-      <c r="F3223" t="inlineStr"/>
-      <c r="G3223" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3224">
-      <c r="A3224" t="inlineStr">
-        <is>
-          <t>2025-07-16 16:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3224" t="inlineStr">
-        <is>
-          <t>MBA Mortgage Market IndexJUL/11</t>
-        </is>
-      </c>
-      <c r="C3224" t="inlineStr"/>
-      <c r="D3224" t="inlineStr"/>
-      <c r="E3224" t="inlineStr"/>
-      <c r="F3224" t="inlineStr"/>
-      <c r="G3224" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3225">
-      <c r="A3225" t="inlineStr">
-        <is>
-          <t>2025-07-16 16:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3225" t="inlineStr">
-        <is>
-          <t>MBA Mortgage Refinance IndexJUL/11</t>
-        </is>
-      </c>
-      <c r="C3225" t="inlineStr"/>
-      <c r="D3225" t="inlineStr"/>
-      <c r="E3225" t="inlineStr"/>
-      <c r="F3225" t="inlineStr"/>
-      <c r="G3225" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3226">
-      <c r="A3226" t="inlineStr">
-        <is>
-          <t>2025-07-16 16:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3226" t="inlineStr">
-        <is>
-          <t>MBA Purchase IndexJUL/11</t>
-        </is>
-      </c>
-      <c r="C3226" t="inlineStr"/>
-      <c r="D3226" t="inlineStr"/>
-      <c r="E3226" t="inlineStr"/>
-      <c r="F3226" t="inlineStr"/>
-      <c r="G3226" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3227">
-      <c r="A3227" t="inlineStr">
-        <is>
-          <t>2025-07-16 16:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3227" t="inlineStr">
-        <is>
-          <t>MBA Purchase IndexJUL/11</t>
-        </is>
-      </c>
-      <c r="C3227" t="inlineStr"/>
-      <c r="D3227" t="inlineStr"/>
-      <c r="E3227" t="inlineStr"/>
-      <c r="F3227" t="inlineStr"/>
-      <c r="G3227" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3228">
-      <c r="A3228" t="inlineStr">
-        <is>
-          <t>2025-07-16 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3228" t="inlineStr">
-        <is>
-          <t>PPI YoYJUN</t>
-        </is>
-      </c>
-      <c r="C3228" t="inlineStr"/>
-      <c r="D3228" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E3228" t="inlineStr"/>
-      <c r="F3228" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="G3228" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3229">
-      <c r="A3229" t="inlineStr">
-        <is>
-          <t>2025-07-16 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3229" t="inlineStr">
-        <is>
-          <t>Core PPI YoYJUN</t>
-        </is>
-      </c>
-      <c r="C3229" t="inlineStr"/>
-      <c r="D3229" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="E3229" t="inlineStr"/>
-      <c r="F3229" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="G3229" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3230">
-      <c r="A3230" t="inlineStr">
-        <is>
-          <t>2025-07-16 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3230" t="inlineStr">
-        <is>
-          <t>PPI YoYJUN</t>
-        </is>
-      </c>
-      <c r="C3230" t="inlineStr"/>
-      <c r="D3230" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E3230" t="inlineStr"/>
-      <c r="F3230" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="G3230" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3231">
-      <c r="A3231" t="inlineStr">
-        <is>
-          <t>2025-07-16 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3231" t="inlineStr">
-        <is>
-          <t>PPI Ex Food, Energy and Trade YoYJUN</t>
-        </is>
-      </c>
-      <c r="C3231" t="inlineStr"/>
-      <c r="D3231" t="inlineStr">
-        <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="E3231" t="inlineStr"/>
-      <c r="F3231" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="G3231" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3232">
-      <c r="A3232" t="inlineStr">
-        <is>
-          <t>2025-07-16 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3232" t="inlineStr">
-        <is>
-          <t>PPI Ex Food, Energy and Trade MoMJUN</t>
-        </is>
-      </c>
-      <c r="C3232" t="inlineStr"/>
-      <c r="D3232" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E3232" t="inlineStr"/>
-      <c r="F3232" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="G3232" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3233">
-      <c r="A3233" t="inlineStr">
-        <is>
-          <t>2025-07-16 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3233" t="inlineStr">
-        <is>
-          <t>PPI Ex Food, Energy and Trade YoYJUN</t>
-        </is>
-      </c>
-      <c r="C3233" t="inlineStr"/>
-      <c r="D3233" t="inlineStr">
-        <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="E3233" t="inlineStr"/>
-      <c r="F3233" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="G3233" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3234">
-      <c r="A3234" t="inlineStr">
-        <is>
-          <t>2025-07-16 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3234" t="inlineStr">
-        <is>
-          <t>Core PPI YoYJUN</t>
-        </is>
-      </c>
-      <c r="C3234" t="inlineStr"/>
-      <c r="D3234" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="E3234" t="inlineStr"/>
-      <c r="F3234" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="G3234" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3235">
-      <c r="A3235" t="inlineStr">
-        <is>
-          <t>2025-07-16 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3235" t="inlineStr">
-        <is>
-          <t>Core PPI MoMJUN</t>
-        </is>
-      </c>
-      <c r="C3235" t="inlineStr"/>
-      <c r="D3235" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E3235" t="inlineStr"/>
-      <c r="F3235" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="G3235" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3236">
-      <c r="A3236" t="inlineStr">
-        <is>
-          <t>2025-07-16 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3236" t="inlineStr">
-        <is>
-          <t>PPI MoMJUN</t>
-        </is>
-      </c>
-      <c r="C3236" t="inlineStr"/>
-      <c r="D3236" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E3236" t="inlineStr"/>
-      <c r="F3236" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="G3236" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3237">
-      <c r="A3237" t="inlineStr">
-        <is>
-          <t>2025-07-16 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3237" t="inlineStr">
-        <is>
-          <t>PPIJUN</t>
-        </is>
-      </c>
-      <c r="C3237" t="inlineStr"/>
-      <c r="D3237" t="inlineStr">
-        <is>
-          <t>148.072</t>
-        </is>
-      </c>
-      <c r="E3237" t="inlineStr"/>
-      <c r="F3237" t="inlineStr">
-        <is>
-          <t>148.9</t>
-        </is>
-      </c>
-      <c r="G3237" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3238">
-      <c r="A3238" t="inlineStr">
-        <is>
-          <t>2025-07-16 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3238" t="inlineStr">
-        <is>
-          <t>PPI Ex Food, Energy and Trade MoMJUN</t>
-        </is>
-      </c>
-      <c r="C3238" t="inlineStr"/>
-      <c r="D3238" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E3238" t="inlineStr"/>
-      <c r="F3238" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="G3238" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3239">
-      <c r="A3239" t="inlineStr">
-        <is>
-          <t>2025-07-16 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3239" t="inlineStr">
-        <is>
-          <t>Core PPI MoMJUN</t>
-        </is>
-      </c>
-      <c r="C3239" t="inlineStr"/>
-      <c r="D3239" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E3239" t="inlineStr"/>
-      <c r="F3239" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="G3239" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3240">
-      <c r="A3240" t="inlineStr">
-        <is>
-          <t>2025-07-16 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3240" t="inlineStr">
-        <is>
-          <t>PPI MoMJUN</t>
-        </is>
-      </c>
-      <c r="C3240" t="inlineStr"/>
-      <c r="D3240" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E3240" t="inlineStr"/>
-      <c r="F3240" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="G3240" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3241">
-      <c r="A3241" t="inlineStr">
-        <is>
-          <t>2025-07-16 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3241" t="inlineStr">
-        <is>
-          <t>PPIJUN</t>
-        </is>
-      </c>
-      <c r="C3241" t="inlineStr"/>
-      <c r="D3241" t="inlineStr">
-        <is>
-          <t>148.072</t>
-        </is>
-      </c>
-      <c r="E3241" t="inlineStr"/>
-      <c r="F3241" t="inlineStr">
-        <is>
-          <t>148.9</t>
-        </is>
-      </c>
-      <c r="G3241" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3242">
-      <c r="A3242" t="inlineStr">
-        <is>
-          <t>2025-07-16 18:45:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3242" t="inlineStr">
-        <is>
-          <t>Capacity UtilizationJUN</t>
-        </is>
-      </c>
-      <c r="C3242" t="inlineStr"/>
-      <c r="D3242" t="inlineStr">
-        <is>
-          <t>77.4%</t>
-        </is>
-      </c>
-      <c r="E3242" t="inlineStr"/>
-      <c r="F3242" t="inlineStr">
-        <is>
-          <t>77.4%</t>
-        </is>
-      </c>
-      <c r="G3242" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3243">
-      <c r="A3243" t="inlineStr">
-        <is>
-          <t>2025-07-16 18:45:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3243" t="inlineStr">
-        <is>
-          <t>Fed Hammack Speech</t>
-        </is>
-      </c>
-      <c r="C3243" t="inlineStr"/>
-      <c r="D3243" t="inlineStr"/>
-      <c r="E3243" t="inlineStr"/>
-      <c r="F3243" t="inlineStr"/>
-      <c r="G3243" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3244">
-      <c r="A3244" t="inlineStr">
-        <is>
-          <t>2025-07-16 18:45:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3244" t="inlineStr">
-        <is>
-          <t>Manufacturing Production YoYJUN</t>
-        </is>
-      </c>
-      <c r="C3244" t="inlineStr"/>
-      <c r="D3244" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E3244" t="inlineStr"/>
-      <c r="F3244" t="inlineStr">
-        <is>
-          <t>1.1%</t>
-        </is>
-      </c>
-      <c r="G3244" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3245">
-      <c r="A3245" t="inlineStr">
-        <is>
-          <t>2025-07-16 18:45:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3245" t="inlineStr">
-        <is>
-          <t>Manufacturing Production YoYJUN</t>
-        </is>
-      </c>
-      <c r="C3245" t="inlineStr"/>
-      <c r="D3245" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E3245" t="inlineStr"/>
-      <c r="F3245" t="inlineStr">
-        <is>
-          <t>1.1%</t>
-        </is>
-      </c>
-      <c r="G3245" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3246">
-      <c r="A3246" t="inlineStr">
-        <is>
-          <t>2025-07-16 18:45:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3246" t="inlineStr">
-        <is>
-          <t>Manufacturing Production MoMJUN</t>
-        </is>
-      </c>
-      <c r="C3246" t="inlineStr"/>
-      <c r="D3246" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E3246" t="inlineStr"/>
-      <c r="F3246" t="inlineStr"/>
-      <c r="G3246" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3247">
-      <c r="A3247" t="inlineStr">
-        <is>
-          <t>2025-07-16 18:45:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3247" t="inlineStr">
-        <is>
-          <t>Fed Hammack Speech</t>
-        </is>
-      </c>
-      <c r="C3247" t="inlineStr"/>
-      <c r="D3247" t="inlineStr"/>
-      <c r="E3247" t="inlineStr"/>
-      <c r="F3247" t="inlineStr"/>
-      <c r="G3247" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3248">
-      <c r="A3248" t="inlineStr">
-        <is>
-          <t>2025-07-16 18:45:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3248" t="inlineStr">
-        <is>
-          <t>Capacity UtilizationJUN</t>
-        </is>
-      </c>
-      <c r="C3248" t="inlineStr"/>
-      <c r="D3248" t="inlineStr">
-        <is>
-          <t>77.4%</t>
-        </is>
-      </c>
-      <c r="E3248" t="inlineStr"/>
-      <c r="F3248" t="inlineStr">
-        <is>
-          <t>77.4%</t>
-        </is>
-      </c>
-      <c r="G3248" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3249">
-      <c r="A3249" t="inlineStr">
-        <is>
-          <t>2025-07-16 18:45:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3249" t="inlineStr">
-        <is>
-          <t>Manufacturing Production MoMJUN</t>
-        </is>
-      </c>
-      <c r="C3249" t="inlineStr"/>
-      <c r="D3249" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E3249" t="inlineStr"/>
-      <c r="F3249" t="inlineStr"/>
-      <c r="G3249" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3250">
-      <c r="A3250" t="inlineStr">
-        <is>
-          <t>2025-07-16 18:45:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3250" t="inlineStr">
-        <is>
-          <t>Industrial Production YoYJUN</t>
-        </is>
-      </c>
-      <c r="C3250" t="inlineStr"/>
-      <c r="D3250" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="E3250" t="inlineStr"/>
-      <c r="F3250" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="G3250" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3251">
-      <c r="A3251" t="inlineStr">
-        <is>
-          <t>2025-07-16 18:45:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3251" t="inlineStr">
-        <is>
-          <t>Industrial Production MoMJUN</t>
-        </is>
-      </c>
-      <c r="C3251" t="inlineStr"/>
-      <c r="D3251" t="inlineStr">
-        <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E3251" t="inlineStr"/>
-      <c r="F3251" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="G3251" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3252">
-      <c r="A3252" t="inlineStr">
-        <is>
-          <t>2025-07-16 18:45:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3252" t="inlineStr">
-        <is>
-          <t>Industrial Production MoMJUN</t>
-        </is>
-      </c>
-      <c r="C3252" t="inlineStr"/>
-      <c r="D3252" t="inlineStr">
-        <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E3252" t="inlineStr"/>
-      <c r="F3252" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="G3252" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3253">
-      <c r="A3253" t="inlineStr">
-        <is>
-          <t>2025-07-16 18:45:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3253" t="inlineStr">
-        <is>
-          <t>Industrial Production YoYJUN</t>
-        </is>
-      </c>
-      <c r="C3253" t="inlineStr"/>
-      <c r="D3253" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="E3253" t="inlineStr"/>
-      <c r="F3253" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="G3253" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3254">
-      <c r="A3254" t="inlineStr">
-        <is>
-          <t>2025-07-16 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3254" t="inlineStr">
-        <is>
-          <t>EIA Gasoline Stocks ChangeJUL/11</t>
-        </is>
-      </c>
-      <c r="C3254" t="inlineStr"/>
-      <c r="D3254" t="inlineStr"/>
-      <c r="E3254" t="inlineStr"/>
-      <c r="F3254" t="inlineStr"/>
-      <c r="G3254" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3255">
-      <c r="A3255" t="inlineStr">
-        <is>
-          <t>2025-07-16 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3255" t="inlineStr">
-        <is>
-          <t>EIA Crude Oil Imports ChangeJUL/11</t>
-        </is>
-      </c>
-      <c r="C3255" t="inlineStr"/>
-      <c r="D3255" t="inlineStr"/>
-      <c r="E3255" t="inlineStr"/>
-      <c r="F3255" t="inlineStr"/>
-      <c r="G3255" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3256">
-      <c r="A3256" t="inlineStr">
-        <is>
-          <t>2025-07-16 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3256" t="inlineStr">
-        <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJUL/11</t>
-        </is>
-      </c>
-      <c r="C3256" t="inlineStr"/>
-      <c r="D3256" t="inlineStr"/>
-      <c r="E3256" t="inlineStr"/>
-      <c r="F3256" t="inlineStr"/>
-      <c r="G3256" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3257">
-      <c r="A3257" t="inlineStr">
-        <is>
-          <t>2025-07-16 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3257" t="inlineStr">
-        <is>
-          <t>EIA Distillate Fuel Production ChangeJUL/11</t>
-        </is>
-      </c>
-      <c r="C3257" t="inlineStr"/>
-      <c r="D3257" t="inlineStr"/>
-      <c r="E3257" t="inlineStr"/>
-      <c r="F3257" t="inlineStr"/>
-      <c r="G3257" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3258">
-      <c r="A3258" t="inlineStr">
-        <is>
-          <t>2025-07-16 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3258" t="inlineStr">
-        <is>
-          <t>EIA Distillate Stocks ChangeJUL/11</t>
-        </is>
-      </c>
-      <c r="C3258" t="inlineStr"/>
-      <c r="D3258" t="inlineStr"/>
-      <c r="E3258" t="inlineStr"/>
-      <c r="F3258" t="inlineStr"/>
-      <c r="G3258" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3259">
-      <c r="A3259" t="inlineStr">
-        <is>
-          <t>2025-07-16 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3259" t="inlineStr">
-        <is>
-          <t>EIA Gasoline Production ChangeJUL/11</t>
-        </is>
-      </c>
-      <c r="C3259" t="inlineStr"/>
-      <c r="D3259" t="inlineStr"/>
-      <c r="E3259" t="inlineStr"/>
-      <c r="F3259" t="inlineStr"/>
-      <c r="G3259" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3260">
-      <c r="A3260" t="inlineStr">
-        <is>
-          <t>2025-07-16 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3260" t="inlineStr">
-        <is>
-          <t>EIA Heating Oil Stocks ChangeJUL/11</t>
-        </is>
-      </c>
-      <c r="C3260" t="inlineStr"/>
-      <c r="D3260" t="inlineStr"/>
-      <c r="E3260" t="inlineStr"/>
-      <c r="F3260" t="inlineStr"/>
-      <c r="G3260" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3261">
-      <c r="A3261" t="inlineStr">
-        <is>
-          <t>2025-07-16 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3261" t="inlineStr">
-        <is>
-          <t>EIA Refinery Crude Runs ChangeJUL/11</t>
-        </is>
-      </c>
-      <c r="C3261" t="inlineStr"/>
-      <c r="D3261" t="inlineStr"/>
-      <c r="E3261" t="inlineStr"/>
-      <c r="F3261" t="inlineStr"/>
-      <c r="G3261" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3262">
-      <c r="A3262" t="inlineStr">
-        <is>
-          <t>2025-07-16 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3262" t="inlineStr">
-        <is>
-          <t>EIA Crude Oil Stocks ChangeJUL/11</t>
-        </is>
-      </c>
-      <c r="C3262" t="inlineStr"/>
-      <c r="D3262" t="inlineStr"/>
-      <c r="E3262" t="inlineStr"/>
-      <c r="F3262" t="inlineStr"/>
-      <c r="G3262" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3263">
-      <c r="A3263" t="inlineStr">
-        <is>
-          <t>2025-07-16 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3263" t="inlineStr">
-        <is>
-          <t>EIA Crude Oil Imports ChangeJUL/11</t>
-        </is>
-      </c>
-      <c r="C3263" t="inlineStr"/>
-      <c r="D3263" t="inlineStr"/>
-      <c r="E3263" t="inlineStr"/>
-      <c r="F3263" t="inlineStr"/>
-      <c r="G3263" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3264">
-      <c r="A3264" t="inlineStr">
-        <is>
-          <t>2025-07-16 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3264" t="inlineStr">
-        <is>
-          <t>EIA Gasoline Stocks ChangeJUL/11</t>
-        </is>
-      </c>
-      <c r="C3264" t="inlineStr"/>
-      <c r="D3264" t="inlineStr"/>
-      <c r="E3264" t="inlineStr"/>
-      <c r="F3264" t="inlineStr"/>
-      <c r="G3264" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3265">
-      <c r="A3265" t="inlineStr">
-        <is>
-          <t>2025-07-16 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3265" t="inlineStr">
-        <is>
-          <t>EIA Distillate Fuel Production ChangeJUL/11</t>
-        </is>
-      </c>
-      <c r="C3265" t="inlineStr"/>
-      <c r="D3265" t="inlineStr"/>
-      <c r="E3265" t="inlineStr"/>
-      <c r="F3265" t="inlineStr"/>
-      <c r="G3265" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3266">
-      <c r="A3266" t="inlineStr">
-        <is>
-          <t>2025-07-16 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3266" t="inlineStr">
-        <is>
-          <t>EIA Refinery Crude Runs ChangeJUL/11</t>
-        </is>
-      </c>
-      <c r="C3266" t="inlineStr"/>
-      <c r="D3266" t="inlineStr"/>
-      <c r="E3266" t="inlineStr"/>
-      <c r="F3266" t="inlineStr"/>
-      <c r="G3266" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3267">
-      <c r="A3267" t="inlineStr">
-        <is>
-          <t>2025-07-16 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3267" t="inlineStr">
-        <is>
-          <t>EIA Distillate Stocks ChangeJUL/11</t>
-        </is>
-      </c>
-      <c r="C3267" t="inlineStr"/>
-      <c r="D3267" t="inlineStr"/>
-      <c r="E3267" t="inlineStr"/>
-      <c r="F3267" t="inlineStr"/>
-      <c r="G3267" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3268">
-      <c r="A3268" t="inlineStr">
-        <is>
-          <t>2025-07-16 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3268" t="inlineStr">
-        <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJUL/11</t>
-        </is>
-      </c>
-      <c r="C3268" t="inlineStr"/>
-      <c r="D3268" t="inlineStr"/>
-      <c r="E3268" t="inlineStr"/>
-      <c r="F3268" t="inlineStr"/>
-      <c r="G3268" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3269">
-      <c r="A3269" t="inlineStr">
-        <is>
-          <t>2025-07-16 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3269" t="inlineStr">
-        <is>
-          <t>EIA Crude Oil Stocks ChangeJUL/11</t>
-        </is>
-      </c>
-      <c r="C3269" t="inlineStr"/>
-      <c r="D3269" t="inlineStr"/>
-      <c r="E3269" t="inlineStr"/>
-      <c r="F3269" t="inlineStr"/>
-      <c r="G3269" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3270">
-      <c r="A3270" t="inlineStr">
-        <is>
-          <t>2025-07-16 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3270" t="inlineStr">
-        <is>
-          <t>EIA Gasoline Production ChangeJUL/11</t>
-        </is>
-      </c>
-      <c r="C3270" t="inlineStr"/>
-      <c r="D3270" t="inlineStr"/>
-      <c r="E3270" t="inlineStr"/>
-      <c r="F3270" t="inlineStr"/>
-      <c r="G3270" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3271">
-      <c r="A3271" t="inlineStr">
-        <is>
-          <t>2025-07-16 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3271" t="inlineStr">
-        <is>
-          <t>EIA Heating Oil Stocks ChangeJUL/11</t>
-        </is>
-      </c>
-      <c r="C3271" t="inlineStr"/>
-      <c r="D3271" t="inlineStr"/>
-      <c r="E3271" t="inlineStr"/>
-      <c r="F3271" t="inlineStr"/>
-      <c r="G3271" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3272">
-      <c r="A3272" t="inlineStr">
-        <is>
-          <t>2025-07-16 21:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3272" t="inlineStr">
-        <is>
-          <t>17-Week Bill Auction</t>
-        </is>
-      </c>
-      <c r="C3272" t="inlineStr"/>
-      <c r="D3272" t="inlineStr"/>
-      <c r="E3272" t="inlineStr"/>
-      <c r="F3272" t="inlineStr"/>
-      <c r="G3272" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3273">
-      <c r="A3273" t="inlineStr">
-        <is>
-          <t>2025-07-16 21:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3273" t="inlineStr">
-        <is>
-          <t>17-Week Bill Auction</t>
-        </is>
-      </c>
-      <c r="C3273" t="inlineStr"/>
-      <c r="D3273" t="inlineStr"/>
-      <c r="E3273" t="inlineStr"/>
-      <c r="F3273" t="inlineStr"/>
-      <c r="G3273" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3274">
-      <c r="A3274" t="inlineStr">
-        <is>
-          <t>2025-07-16 23:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3274" t="inlineStr">
-        <is>
-          <t>Fed Beige Book</t>
-        </is>
-      </c>
-      <c r="C3274" t="inlineStr"/>
-      <c r="D3274" t="inlineStr"/>
-      <c r="E3274" t="inlineStr"/>
-      <c r="F3274" t="inlineStr"/>
-      <c r="G3274" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3275">
-      <c r="A3275" t="inlineStr">
-        <is>
-          <t>2025-07-16 23:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3275" t="inlineStr">
-        <is>
-          <t>Fed Beige Book</t>
-        </is>
-      </c>
-      <c r="C3275" t="inlineStr"/>
-      <c r="D3275" t="inlineStr"/>
-      <c r="E3275" t="inlineStr"/>
-      <c r="F3275" t="inlineStr"/>
-      <c r="G3275" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3276">
-      <c r="A3276" t="inlineStr">
-        <is>
-          <t>2025-07-17 04:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3276" t="inlineStr">
-        <is>
-          <t>Fed Williams Speech</t>
-        </is>
-      </c>
-      <c r="C3276" t="inlineStr"/>
-      <c r="D3276" t="inlineStr"/>
-      <c r="E3276" t="inlineStr"/>
-      <c r="F3276" t="inlineStr"/>
-      <c r="G3276" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3277">
-      <c r="A3277" t="inlineStr">
-        <is>
-          <t>2025-07-17 04:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3277" t="inlineStr">
-        <is>
-          <t>Fed Williams Speech</t>
-        </is>
-      </c>
-      <c r="C3277" t="inlineStr"/>
-      <c r="D3277" t="inlineStr"/>
-      <c r="E3277" t="inlineStr"/>
-      <c r="F3277" t="inlineStr"/>
-      <c r="G3277" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3278">
-      <c r="A3278" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3278" t="inlineStr">
-        <is>
-          <t>Retail Sales MoMJUN</t>
-        </is>
-      </c>
-      <c r="C3278" t="inlineStr"/>
-      <c r="D3278" t="inlineStr">
-        <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="E3278" t="inlineStr"/>
-      <c r="F3278" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="G3278" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3279">
-      <c r="A3279" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3279" t="inlineStr">
-        <is>
-          <t>Export Prices MoMJUN</t>
-        </is>
-      </c>
-      <c r="C3279" t="inlineStr"/>
-      <c r="D3279" t="inlineStr">
-        <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="E3279" t="inlineStr"/>
-      <c r="F3279" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="G3279" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3280">
-      <c r="A3280" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3280" t="inlineStr">
-        <is>
-          <t>Import Prices MoMJUN</t>
-        </is>
-      </c>
-      <c r="C3280" t="inlineStr"/>
-      <c r="D3280" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="E3280" t="inlineStr"/>
-      <c r="F3280" t="inlineStr"/>
-      <c r="G3280" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3281">
-      <c r="A3281" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3281" t="inlineStr">
-        <is>
-          <t>Initial Jobless ClaimsJUL/12</t>
-        </is>
-      </c>
-      <c r="C3281" t="inlineStr"/>
-      <c r="D3281" t="inlineStr"/>
-      <c r="E3281" t="inlineStr"/>
-      <c r="F3281" t="inlineStr"/>
-      <c r="G3281" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3282">
-      <c r="A3282" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3282" t="inlineStr">
-        <is>
-          <t>Philadelphia Fed Manufacturing IndexJUL</t>
-        </is>
-      </c>
-      <c r="C3282" t="inlineStr"/>
-      <c r="D3282" t="inlineStr">
-        <is>
-          <t>-4.0</t>
-        </is>
-      </c>
-      <c r="E3282" t="inlineStr"/>
-      <c r="F3282" t="inlineStr"/>
-      <c r="G3282" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3283">
-      <c r="A3283" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3283" t="inlineStr">
-        <is>
-          <t>Continuing Jobless ClaimsJUL/05</t>
-        </is>
-      </c>
-      <c r="C3283" t="inlineStr"/>
-      <c r="D3283" t="inlineStr"/>
-      <c r="E3283" t="inlineStr"/>
-      <c r="F3283" t="inlineStr">
-        <is>
-          <t>1970.0K</t>
-        </is>
-      </c>
-      <c r="G3283" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3284">
-      <c r="A3284" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3284" t="inlineStr">
-        <is>
-          <t>Retail Sales Ex Autos MoMJUN</t>
-        </is>
-      </c>
-      <c r="C3284" t="inlineStr"/>
-      <c r="D3284" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
-      <c r="E3284" t="inlineStr"/>
-      <c r="F3284" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="G3284" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3285">
-      <c r="A3285" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3285" t="inlineStr">
-        <is>
-          <t>Retail Sales Ex Autos MoMJUN</t>
-        </is>
-      </c>
-      <c r="C3285" t="inlineStr"/>
-      <c r="D3285" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
-      <c r="E3285" t="inlineStr"/>
-      <c r="F3285" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="G3285" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3286">
-      <c r="A3286" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3286" t="inlineStr">
-        <is>
-          <t>Export Prices YoYJUN</t>
-        </is>
-      </c>
-      <c r="C3286" t="inlineStr"/>
-      <c r="D3286" t="inlineStr">
-        <is>
-          <t>1.7%</t>
-        </is>
-      </c>
-      <c r="E3286" t="inlineStr"/>
-      <c r="F3286" t="inlineStr"/>
-      <c r="G3286" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3287">
-      <c r="A3287" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3287" t="inlineStr">
-        <is>
-          <t>Import Prices YoYJUN</t>
-        </is>
-      </c>
-      <c r="C3287" t="inlineStr"/>
-      <c r="D3287" t="inlineStr"/>
-      <c r="E3287" t="inlineStr"/>
-      <c r="F3287" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="G3287" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3288">
-      <c r="A3288" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3288" t="inlineStr">
-        <is>
-          <t>Jobless Claims 4-week AverageJUL/12</t>
-        </is>
-      </c>
-      <c r="C3288" t="inlineStr"/>
-      <c r="D3288" t="inlineStr"/>
-      <c r="E3288" t="inlineStr"/>
-      <c r="F3288" t="inlineStr"/>
-      <c r="G3288" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3289">
-      <c r="A3289" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3289" t="inlineStr">
-        <is>
-          <t>Philly Fed Business ConditionsJUL</t>
-        </is>
-      </c>
-      <c r="C3289" t="inlineStr"/>
-      <c r="D3289" t="inlineStr"/>
-      <c r="E3289" t="inlineStr"/>
-      <c r="F3289" t="inlineStr"/>
-      <c r="G3289" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3290">
-      <c r="A3290" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3290" t="inlineStr">
-        <is>
-          <t>Philly Fed CAPEX IndexJUL</t>
-        </is>
-      </c>
-      <c r="C3290" t="inlineStr"/>
-      <c r="D3290" t="inlineStr">
-        <is>
-          <t>14.50</t>
-        </is>
-      </c>
-      <c r="E3290" t="inlineStr"/>
-      <c r="F3290" t="inlineStr"/>
-      <c r="G3290" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3291">
-      <c r="A3291" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3291" t="inlineStr">
-        <is>
-          <t>Philly Fed EmploymentJUL</t>
-        </is>
-      </c>
-      <c r="C3291" t="inlineStr"/>
-      <c r="D3291" t="inlineStr">
-        <is>
-          <t>-9.8</t>
-        </is>
-      </c>
-      <c r="E3291" t="inlineStr"/>
-      <c r="F3291" t="inlineStr"/>
-      <c r="G3291" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3292">
-      <c r="A3292" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3292" t="inlineStr">
-        <is>
-          <t>Philly Fed New OrdersJUL</t>
-        </is>
-      </c>
-      <c r="C3292" t="inlineStr"/>
-      <c r="D3292" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="E3292" t="inlineStr"/>
-      <c r="F3292" t="inlineStr"/>
-      <c r="G3292" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3293">
-      <c r="A3293" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3293" t="inlineStr">
-        <is>
-          <t>Philly Fed Prices PaidJUL</t>
-        </is>
-      </c>
-      <c r="C3293" t="inlineStr"/>
-      <c r="D3293" t="inlineStr">
-        <is>
-          <t>41.40</t>
-        </is>
-      </c>
-      <c r="E3293" t="inlineStr"/>
-      <c r="F3293" t="inlineStr"/>
-      <c r="G3293" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3294">
-      <c r="A3294" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3294" t="inlineStr">
-        <is>
-          <t>Retail Sales Ex Gas/Autos MoMJUN</t>
-        </is>
-      </c>
-      <c r="C3294" t="inlineStr"/>
-      <c r="D3294" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E3294" t="inlineStr"/>
-      <c r="F3294" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="G3294" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3295">
-      <c r="A3295" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3295" t="inlineStr">
-        <is>
-          <t>Retail Sales YoYJUN</t>
-        </is>
-      </c>
-      <c r="C3295" t="inlineStr"/>
-      <c r="D3295" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="E3295" t="inlineStr"/>
-      <c r="F3295" t="inlineStr">
-        <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="G3295" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3296">
-      <c r="A3296" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3296" t="inlineStr">
-        <is>
-          <t>Retail Sales Control Group MoMJUN</t>
-        </is>
-      </c>
-      <c r="C3296" t="inlineStr"/>
-      <c r="D3296" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E3296" t="inlineStr"/>
-      <c r="F3296" t="inlineStr"/>
-      <c r="G3296" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3297">
-      <c r="A3297" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3297" t="inlineStr">
-        <is>
-          <t>Philly Fed Business ConditionsJUL</t>
-        </is>
-      </c>
-      <c r="C3297" t="inlineStr"/>
-      <c r="D3297" t="inlineStr"/>
-      <c r="E3297" t="inlineStr"/>
-      <c r="F3297" t="inlineStr"/>
-      <c r="G3297" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3298">
-      <c r="A3298" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3298" t="inlineStr">
-        <is>
-          <t>Export Prices YoYJUN</t>
-        </is>
-      </c>
-      <c r="C3298" t="inlineStr"/>
-      <c r="D3298" t="inlineStr">
-        <is>
-          <t>1.7%</t>
-        </is>
-      </c>
-      <c r="E3298" t="inlineStr"/>
-      <c r="F3298" t="inlineStr"/>
-      <c r="G3298" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3299">
-      <c r="A3299" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3299" t="inlineStr">
-        <is>
-          <t>Continuing Jobless ClaimsJUL/05</t>
-        </is>
-      </c>
-      <c r="C3299" t="inlineStr"/>
-      <c r="D3299" t="inlineStr"/>
-      <c r="E3299" t="inlineStr"/>
-      <c r="F3299" t="inlineStr">
-        <is>
-          <t>1970.0K</t>
-        </is>
-      </c>
-      <c r="G3299" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3300">
-      <c r="A3300" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3300" t="inlineStr">
-        <is>
-          <t>Retail Sales MoMJUN</t>
-        </is>
-      </c>
-      <c r="C3300" t="inlineStr"/>
-      <c r="D3300" t="inlineStr">
-        <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="E3300" t="inlineStr"/>
-      <c r="F3300" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="G3300" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3301">
-      <c r="A3301" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3301" t="inlineStr">
-        <is>
-          <t>Initial Jobless ClaimsJUL/12</t>
-        </is>
-      </c>
-      <c r="C3301" t="inlineStr"/>
-      <c r="D3301" t="inlineStr"/>
-      <c r="E3301" t="inlineStr"/>
-      <c r="F3301" t="inlineStr"/>
-      <c r="G3301" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3302">
-      <c r="A3302" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3302" t="inlineStr">
-        <is>
-          <t>Import Prices MoMJUN</t>
-        </is>
-      </c>
-      <c r="C3302" t="inlineStr"/>
-      <c r="D3302" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="E3302" t="inlineStr"/>
-      <c r="F3302" t="inlineStr"/>
-      <c r="G3302" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3303">
-      <c r="A3303" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3303" t="inlineStr">
-        <is>
-          <t>Jobless Claims 4-week AverageJUL/12</t>
-        </is>
-      </c>
-      <c r="C3303" t="inlineStr"/>
-      <c r="D3303" t="inlineStr"/>
-      <c r="E3303" t="inlineStr"/>
-      <c r="F3303" t="inlineStr"/>
-      <c r="G3303" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3304">
-      <c r="A3304" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3304" t="inlineStr">
-        <is>
-          <t>Export Prices MoMJUN</t>
-        </is>
-      </c>
-      <c r="C3304" t="inlineStr"/>
-      <c r="D3304" t="inlineStr">
-        <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="E3304" t="inlineStr"/>
-      <c r="F3304" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="G3304" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3305">
-      <c r="A3305" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3305" t="inlineStr">
-        <is>
-          <t>Philly Fed New OrdersJUL</t>
-        </is>
-      </c>
-      <c r="C3305" t="inlineStr"/>
-      <c r="D3305" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="E3305" t="inlineStr"/>
-      <c r="F3305" t="inlineStr"/>
-      <c r="G3305" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3306">
-      <c r="A3306" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3306" t="inlineStr">
-        <is>
-          <t>Philly Fed CAPEX IndexJUL</t>
-        </is>
-      </c>
-      <c r="C3306" t="inlineStr"/>
-      <c r="D3306" t="inlineStr">
-        <is>
-          <t>14.50</t>
-        </is>
-      </c>
-      <c r="E3306" t="inlineStr"/>
-      <c r="F3306" t="inlineStr"/>
-      <c r="G3306" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3307">
-      <c r="A3307" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3307" t="inlineStr">
-        <is>
-          <t>Philadelphia Fed Manufacturing IndexJUL</t>
-        </is>
-      </c>
-      <c r="C3307" t="inlineStr"/>
-      <c r="D3307" t="inlineStr">
-        <is>
-          <t>-4.0</t>
-        </is>
-      </c>
-      <c r="E3307" t="inlineStr"/>
-      <c r="F3307" t="inlineStr"/>
-      <c r="G3307" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3308">
-      <c r="A3308" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3308" t="inlineStr">
-        <is>
-          <t>Import Prices YoYJUN</t>
-        </is>
-      </c>
-      <c r="C3308" t="inlineStr"/>
-      <c r="D3308" t="inlineStr"/>
-      <c r="E3308" t="inlineStr"/>
-      <c r="F3308" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="G3308" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3309">
-      <c r="A3309" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3309" t="inlineStr">
-        <is>
-          <t>Philly Fed EmploymentJUL</t>
-        </is>
-      </c>
-      <c r="C3309" t="inlineStr"/>
-      <c r="D3309" t="inlineStr">
-        <is>
-          <t>-9.8</t>
-        </is>
-      </c>
-      <c r="E3309" t="inlineStr"/>
-      <c r="F3309" t="inlineStr"/>
-      <c r="G3309" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3310">
-      <c r="A3310" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3310" t="inlineStr">
-        <is>
-          <t>Retail Sales Control Group MoMJUN</t>
-        </is>
-      </c>
-      <c r="C3310" t="inlineStr"/>
-      <c r="D3310" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E3310" t="inlineStr"/>
-      <c r="F3310" t="inlineStr"/>
-      <c r="G3310" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3311">
-      <c r="A3311" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3311" t="inlineStr">
-        <is>
-          <t>Retail Sales Ex Gas/Autos MoMJUN</t>
-        </is>
-      </c>
-      <c r="C3311" t="inlineStr"/>
-      <c r="D3311" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E3311" t="inlineStr"/>
-      <c r="F3311" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="G3311" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3312">
-      <c r="A3312" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3312" t="inlineStr">
-        <is>
-          <t>Philly Fed Prices PaidJUL</t>
-        </is>
-      </c>
-      <c r="C3312" t="inlineStr"/>
-      <c r="D3312" t="inlineStr">
-        <is>
-          <t>41.40</t>
-        </is>
-      </c>
-      <c r="E3312" t="inlineStr"/>
-      <c r="F3312" t="inlineStr"/>
-      <c r="G3312" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3313">
-      <c r="A3313" t="inlineStr">
-        <is>
-          <t>2025-07-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3313" t="inlineStr">
-        <is>
-          <t>Retail Sales YoYJUN</t>
-        </is>
-      </c>
-      <c r="C3313" t="inlineStr"/>
-      <c r="D3313" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="E3313" t="inlineStr"/>
-      <c r="F3313" t="inlineStr">
-        <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="G3313" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3314">
-      <c r="A3314" t="inlineStr">
-        <is>
-          <t>2025-07-17 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3314" t="inlineStr">
-        <is>
-          <t>Retail Inventories Ex Autos MoMMAY</t>
-        </is>
-      </c>
-      <c r="C3314" t="inlineStr"/>
-      <c r="D3314" t="inlineStr"/>
-      <c r="E3314" t="inlineStr"/>
-      <c r="F3314" t="inlineStr"/>
-      <c r="G3314" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3315">
-      <c r="A3315" t="inlineStr">
-        <is>
-          <t>2025-07-17 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3315" t="inlineStr">
-        <is>
-          <t>NAHB Housing Market IndexJUL</t>
-        </is>
-      </c>
-      <c r="C3315" t="inlineStr"/>
-      <c r="D3315" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E3315" t="inlineStr"/>
-      <c r="F3315" t="inlineStr"/>
-      <c r="G3315" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3316">
-      <c r="A3316" t="inlineStr">
-        <is>
-          <t>2025-07-17 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3316" t="inlineStr">
-        <is>
-          <t>Business Inventories MoMMAY</t>
-        </is>
-      </c>
-      <c r="C3316" t="inlineStr"/>
-      <c r="D3316" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="E3316" t="inlineStr"/>
-      <c r="F3316" t="inlineStr"/>
-      <c r="G3316" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3317">
-      <c r="A3317" t="inlineStr">
-        <is>
-          <t>2025-07-17 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3317" t="inlineStr">
-        <is>
-          <t>NAHB Housing Market IndexJUL</t>
-        </is>
-      </c>
-      <c r="C3317" t="inlineStr"/>
-      <c r="D3317" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E3317" t="inlineStr"/>
-      <c r="F3317" t="inlineStr"/>
-      <c r="G3317" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3318">
-      <c r="A3318" t="inlineStr">
-        <is>
-          <t>2025-07-17 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3318" t="inlineStr">
-        <is>
-          <t>Retail Inventories Ex Autos MoMMAY</t>
-        </is>
-      </c>
-      <c r="C3318" t="inlineStr"/>
-      <c r="D3318" t="inlineStr"/>
-      <c r="E3318" t="inlineStr"/>
-      <c r="F3318" t="inlineStr"/>
-      <c r="G3318" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3319">
-      <c r="A3319" t="inlineStr">
-        <is>
-          <t>2025-07-17 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3319" t="inlineStr">
-        <is>
-          <t>Business Inventories MoMMAY</t>
-        </is>
-      </c>
-      <c r="C3319" t="inlineStr"/>
-      <c r="D3319" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="E3319" t="inlineStr"/>
-      <c r="F3319" t="inlineStr"/>
-      <c r="G3319" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3320">
-      <c r="A3320" t="inlineStr">
-        <is>
-          <t>2025-07-17 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3320" t="inlineStr">
-        <is>
-          <t>EIA Natural Gas Stocks ChangeJUL/11</t>
-        </is>
-      </c>
-      <c r="C3320" t="inlineStr"/>
-      <c r="D3320" t="inlineStr"/>
-      <c r="E3320" t="inlineStr"/>
-      <c r="F3320" t="inlineStr"/>
-      <c r="G3320" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3321">
-      <c r="A3321" t="inlineStr">
-        <is>
-          <t>2025-07-17 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3321" t="inlineStr">
-        <is>
-          <t>EIA Natural Gas Stocks ChangeJUL/11</t>
-        </is>
-      </c>
-      <c r="C3321" t="inlineStr"/>
-      <c r="D3321" t="inlineStr"/>
-      <c r="E3321" t="inlineStr"/>
-      <c r="F3321" t="inlineStr"/>
-      <c r="G3321" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3322">
-      <c r="A3322" t="inlineStr">
-        <is>
-          <t>2025-07-17 21:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3322" t="inlineStr">
-        <is>
-          <t>4-Week Bill Auction</t>
-        </is>
-      </c>
-      <c r="C3322" t="inlineStr"/>
-      <c r="D3322" t="inlineStr"/>
-      <c r="E3322" t="inlineStr"/>
-      <c r="F3322" t="inlineStr"/>
-      <c r="G3322" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3323">
-      <c r="A3323" t="inlineStr">
-        <is>
-          <t>2025-07-17 21:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3323" t="inlineStr">
-        <is>
-          <t>8-Week Bill Auction</t>
-        </is>
-      </c>
-      <c r="C3323" t="inlineStr"/>
-      <c r="D3323" t="inlineStr"/>
-      <c r="E3323" t="inlineStr"/>
-      <c r="F3323" t="inlineStr"/>
-      <c r="G3323" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3324">
-      <c r="A3324" t="inlineStr">
-        <is>
-          <t>2025-07-17 21:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3324" t="inlineStr">
-        <is>
-          <t>4-Week Bill Auction</t>
-        </is>
-      </c>
-      <c r="C3324" t="inlineStr"/>
-      <c r="D3324" t="inlineStr"/>
-      <c r="E3324" t="inlineStr"/>
-      <c r="F3324" t="inlineStr"/>
-      <c r="G3324" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3325">
-      <c r="A3325" t="inlineStr">
-        <is>
-          <t>2025-07-17 21:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3325" t="inlineStr">
-        <is>
-          <t>8-Week Bill Auction</t>
-        </is>
-      </c>
-      <c r="C3325" t="inlineStr"/>
-      <c r="D3325" t="inlineStr"/>
-      <c r="E3325" t="inlineStr"/>
-      <c r="F3325" t="inlineStr"/>
-      <c r="G3325" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3326">
-      <c r="A3326" t="inlineStr">
-        <is>
-          <t>2025-07-17 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3326" t="inlineStr">
-        <is>
-          <t>15-Year Mortgage RateJUL/17</t>
-        </is>
-      </c>
-      <c r="C3326" t="inlineStr"/>
-      <c r="D3326" t="inlineStr"/>
-      <c r="E3326" t="inlineStr"/>
-      <c r="F3326" t="inlineStr"/>
-      <c r="G3326" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3327">
-      <c r="A3327" t="inlineStr">
-        <is>
-          <t>2025-07-17 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3327" t="inlineStr">
-        <is>
-          <t>30-Year Mortgage RateJUL/17</t>
-        </is>
-      </c>
-      <c r="C3327" t="inlineStr"/>
-      <c r="D3327" t="inlineStr"/>
-      <c r="E3327" t="inlineStr"/>
-      <c r="F3327" t="inlineStr"/>
-      <c r="G3327" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3328">
-      <c r="A3328" t="inlineStr">
-        <is>
-          <t>2025-07-17 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3328" t="inlineStr">
-        <is>
-          <t>15-Year Mortgage RateJUL/17</t>
-        </is>
-      </c>
-      <c r="C3328" t="inlineStr"/>
-      <c r="D3328" t="inlineStr"/>
-      <c r="E3328" t="inlineStr"/>
-      <c r="F3328" t="inlineStr"/>
-      <c r="G3328" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3329">
-      <c r="A3329" t="inlineStr">
-        <is>
-          <t>2025-07-17 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3329" t="inlineStr">
-        <is>
-          <t>30-Year Mortgage RateJUL/17</t>
-        </is>
-      </c>
-      <c r="C3329" t="inlineStr"/>
-      <c r="D3329" t="inlineStr"/>
-      <c r="E3329" t="inlineStr"/>
-      <c r="F3329" t="inlineStr"/>
-      <c r="G3329" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3330">
-      <c r="A3330" t="inlineStr">
-        <is>
-          <t>2025-07-18 01:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3330" t="inlineStr">
-        <is>
-          <t>Net Long-term TIC FlowsMAY</t>
-        </is>
-      </c>
-      <c r="C3330" t="inlineStr"/>
-      <c r="D3330" t="inlineStr">
-        <is>
-          <t>$-7.8B</t>
-        </is>
-      </c>
-      <c r="E3330" t="inlineStr"/>
-      <c r="F3330" t="inlineStr"/>
-      <c r="G3330" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3331">
-      <c r="A3331" t="inlineStr">
-        <is>
-          <t>2025-07-18 01:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3331" t="inlineStr">
-        <is>
-          <t>Foreign Bond InvestmentMAY</t>
-        </is>
-      </c>
-      <c r="C3331" t="inlineStr"/>
-      <c r="D3331" t="inlineStr">
-        <is>
-          <t>$-40.8B</t>
-        </is>
-      </c>
-      <c r="E3331" t="inlineStr"/>
-      <c r="F3331" t="inlineStr"/>
-      <c r="G3331" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3332">
-      <c r="A3332" t="inlineStr">
-        <is>
-          <t>2025-07-18 01:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3332" t="inlineStr">
-        <is>
-          <t>Overall Net Capital FlowsMAY</t>
-        </is>
-      </c>
-      <c r="C3332" t="inlineStr"/>
-      <c r="D3332" t="inlineStr">
-        <is>
-          <t>$-14.2B</t>
-        </is>
-      </c>
-      <c r="E3332" t="inlineStr"/>
-      <c r="F3332" t="inlineStr"/>
-      <c r="G3332" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3333">
-      <c r="A3333" t="inlineStr">
-        <is>
-          <t>2025-07-18 01:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3333" t="inlineStr">
-        <is>
-          <t>Overall Net Capital FlowsMAY</t>
-        </is>
-      </c>
-      <c r="C3333" t="inlineStr"/>
-      <c r="D3333" t="inlineStr">
-        <is>
-          <t>$-14.2B</t>
-        </is>
-      </c>
-      <c r="E3333" t="inlineStr"/>
-      <c r="F3333" t="inlineStr"/>
-      <c r="G3333" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3334">
-      <c r="A3334" t="inlineStr">
-        <is>
-          <t>2025-07-18 01:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3334" t="inlineStr">
-        <is>
-          <t>Net Long-term TIC FlowsMAY</t>
-        </is>
-      </c>
-      <c r="C3334" t="inlineStr"/>
-      <c r="D3334" t="inlineStr">
-        <is>
-          <t>$-7.8B</t>
-        </is>
-      </c>
-      <c r="E3334" t="inlineStr"/>
-      <c r="F3334" t="inlineStr"/>
-      <c r="G3334" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3335">
-      <c r="A3335" t="inlineStr">
-        <is>
-          <t>2025-07-18 01:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3335" t="inlineStr">
-        <is>
-          <t>Foreign Bond InvestmentMAY</t>
-        </is>
-      </c>
-      <c r="C3335" t="inlineStr"/>
-      <c r="D3335" t="inlineStr">
-        <is>
-          <t>$-40.8B</t>
-        </is>
-      </c>
-      <c r="E3335" t="inlineStr"/>
-      <c r="F3335" t="inlineStr"/>
-      <c r="G3335" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3336">
-      <c r="A3336" t="inlineStr">
-        <is>
-          <t>2025-07-18 02:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3336" t="inlineStr">
-        <is>
-          <t>Fed Balance SheetJUL/16</t>
-        </is>
-      </c>
-      <c r="C3336" t="inlineStr"/>
-      <c r="D3336" t="inlineStr"/>
-      <c r="E3336" t="inlineStr"/>
-      <c r="F3336" t="inlineStr"/>
-      <c r="G3336" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3337">
-      <c r="A3337" t="inlineStr">
-        <is>
-          <t>2025-07-18 02:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B3337" t="inlineStr">
-        <is>
-          <t>Fed Balance SheetJUL/16</t>
-        </is>
-      </c>
-      <c r="C3337" t="inlineStr"/>
-      <c r="D3337" t="inlineStr"/>
-      <c r="E3337" t="inlineStr"/>
-      <c r="F3337" t="inlineStr"/>
-      <c r="G3337" t="n">
-        <v>3</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
